--- a/PCDN域名URL关键字.xlsx
+++ b/PCDN域名URL关键字.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileSharing readOnlyRecommended="1"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tencent\1520085249\FileRecv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\QQ文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:201_{88EBFEE7-ADAA-4107-877C-EE063A009584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:201_{53E3FF66-0C17-402D-9D7E-59216C8EC083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" activeTab="2" xr2:uid="{635FD1CB-08EF-4A62-AA24-FB7602255245}"/>
   </bookViews>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="569">
   <si>
     <t>序号</t>
   </si>
@@ -1718,54 +1719,6 @@
   </si>
   <si>
     <t>点击访问作者知乎</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">『哥哥科技』  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FFFF0066"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>点击访问B站</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>QQ交流群：680464365</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-点击加群 有海量资源</t>
-    </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -1875,12 +1828,165 @@
     <t>黄底慎用：已确认，会误伤普通应用</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>英伟达</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>international-gfe.download.nvidia.cn.global.ogslb.com</t>
+  </si>
+  <si>
+    <t>international-gfe.download.nvidia.cn.zengslb.com</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>QQ交流群：680464365</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>点击加群 有海量资源</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>『哥哥</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="8" tint="0.39997558519241921"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>科技</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>』</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FFFF0066"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>点击访问B站</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>网易易盾</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜在误伤</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>建议用长版，防误伤</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI说慎用</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dispatch</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>建议屏蔽</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太短慎用</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>诊断业务</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能是微信?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="57">
+  <fonts count="63">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2357,6 +2463,59 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="8" tint="0.39997558519241921"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0066"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0066"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="37">
     <fill>
@@ -2810,7 +2969,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2940,6 +3099,105 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="42" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2961,119 +3219,38 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="42" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3855,16 +4032,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="42.9" customHeight="1">
-      <c r="A1" s="74" t="s">
-        <v>533</v>
+      <c r="A1" s="64" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="60.45" customHeight="1">
-      <c r="A2" s="73" t="s">
-        <v>534</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>555</v>
+      <c r="A2" s="87" t="s">
+        <v>558</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3892,7 +4069,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="64"/>
+      <c r="A10" s="56"/>
       <c r="D10" t="s">
         <v>528</v>
       </c>
@@ -3907,7 +4084,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3932,21 +4109,22 @@
       <c r="A17" t="s">
         <v>526</v>
       </c>
-      <c r="D17" s="75" t="s">
+      <c r="D17" s="65" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="B19" s="84" t="s">
-        <v>554</v>
+      <c r="B19" s="72" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="IfTHkocq5mqttdUsTAmFkPsRJCUb9PIrhje5EQh0Bqzvjj1AIYNAqwdR3LG9tHIffdtgiAASaGncAIXW6gBUmw==" saltValue="+2aw8t5u3EP/Q1ySvG4aOA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" insertColumns="0" insertRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="http://qm.qq.com/cgi-bin/qm/qr?_wv=1027&amp;k=EWLVxRjsXbJYF3f2roWuEdBg6WQbn2eU&amp;authKey=cBIvoWMHZggA3dfJRSXK8YiThJpjlbR0bVqYMjWFBaZAePQJPvPWh3bxWhc5VUgj&amp;noverify=0&amp;group_code=680464365" xr:uid="{32AB89CA-61C1-4DD7-8B95-E91924B9D322}"/>
-    <hyperlink ref="A1" r:id="rId2" display="『哥哥科技』" xr:uid="{9EF32144-521B-4950-AE15-70DA5D0081D6}"/>
-    <hyperlink ref="D17" r:id="rId3" xr:uid="{B96BC5BE-4A8D-4A8F-A8FE-74CA9E53C7B5}"/>
+    <hyperlink ref="A1" r:id="rId1" display="『哥哥科技』" xr:uid="{9EF32144-521B-4950-AE15-70DA5D0081D6}"/>
+    <hyperlink ref="D17" r:id="rId2" xr:uid="{B96BC5BE-4A8D-4A8F-A8FE-74CA9E53C7B5}"/>
+    <hyperlink ref="A2" r:id="rId3" display="https://qun.qq.com/universal-share/share?ac=1&amp;authKey=%2FWJ%2F4NS6lNp1cyU2a1kUo%2F%2FEfq8vD6q7SXUux2UosjZ%2BialqZVNe%2Bk3w1YoOUR3b&amp;busi_data=eyJncm91cENvZGUiOiI2ODA0NjQzNjUiLCJ0b2tlbiI6IkI5ZHVYaHJnSGlZZEpzSkRhamdOZFZaNy9aZFJ1L1JwNGpZYWNJWTJJRThGYjBoVjN6RUxhUkcvV0h4eHBwV2siLCJ1aW4iOiIxNTIwMDg1MjQ5In0%3D&amp;data=iHLL1DGOGIhddoSRjGmI9D2bMbNLa4vwx5YfZQAzvPM0sAuYo67cPN4265_UAPSpbgqWLVl8vmWBZVREf_Qg-g&amp;svctype=4&amp;tempid=h5_group_info" xr:uid="{32AB89CA-61C1-4DD7-8B95-E91924B9D322}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId4"/>
@@ -3966,7 +4144,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBFF6F1-A409-4FB7-99BD-5BD2847458F8}">
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="7.92578125" style="1" customWidth="1"/>
@@ -3995,10 +4173,10 @@
         <v>219</v>
       </c>
       <c r="H1" s="3"/>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="J1" s="43"/>
+      <c r="J1" s="76"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="22">
@@ -4010,18 +4188,18 @@
       <c r="C2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="78" t="s">
         <v>500</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="79" t="s">
         <v>235</v>
       </c>
-      <c r="G2" s="46"/>
+      <c r="G2" s="79"/>
       <c r="H2" s="12"/>
-      <c r="I2" s="47" t="s">
-        <v>556</v>
-      </c>
-      <c r="J2" s="47"/>
+      <c r="I2" s="80" t="s">
+        <v>554</v>
+      </c>
+      <c r="J2" s="80"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="22">
@@ -4033,7 +4211,7 @@
       <c r="C3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="45"/>
+      <c r="D3" s="78"/>
       <c r="E3" s="1">
         <v>90</v>
       </c>
@@ -4046,10 +4224,10 @@
       <c r="H3" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="I3" s="48" t="s">
+      <c r="I3" s="81" t="s">
         <v>234</v>
       </c>
-      <c r="J3" s="48"/>
+      <c r="J3" s="81"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="22">
@@ -4061,23 +4239,23 @@
       <c r="C4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="45"/>
+      <c r="D4" s="78"/>
       <c r="E4" s="1">
         <v>91</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="91" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="92" t="s">
         <v>116</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="I4" s="49" t="s">
+        <v>566</v>
+      </c>
+      <c r="I4" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="J4" s="49"/>
+      <c r="J4" s="82"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="12">
@@ -4113,15 +4291,15 @@
       <c r="E6" s="1">
         <v>93</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="75" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="48" t="s">
         <v>118</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="80" t="s">
-        <v>548</v>
+      <c r="I6" s="84" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4134,7 +4312,7 @@
       <c r="C7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="56" t="s">
+      <c r="D7" s="49" t="s">
         <v>493</v>
       </c>
       <c r="E7" s="1">
@@ -4147,7 +4325,7 @@
         <v>119</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="80"/>
+      <c r="I7" s="84"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="22">
@@ -4159,7 +4337,7 @@
       <c r="C8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="56" t="s">
+      <c r="D8" s="49" t="s">
         <v>493</v>
       </c>
       <c r="E8" s="1">
@@ -4172,7 +4350,7 @@
         <v>120</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="80"/>
+      <c r="I8" s="84"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="23">
@@ -4184,7 +4362,7 @@
       <c r="C9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="D9" s="49" t="s">
         <v>493</v>
       </c>
       <c r="E9" s="1">
@@ -4197,7 +4375,7 @@
         <v>121</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="80"/>
+      <c r="I9" s="84"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="22">
@@ -4209,7 +4387,7 @@
       <c r="C10" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="49" t="s">
         <v>493</v>
       </c>
       <c r="E10" s="22">
@@ -4222,7 +4400,7 @@
         <v>122</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="80"/>
+      <c r="I10" s="84"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="22">
@@ -4234,7 +4412,7 @@
       <c r="C11" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="56" t="s">
+      <c r="D11" s="49" t="s">
         <v>493</v>
       </c>
       <c r="E11" s="22">
@@ -4258,7 +4436,7 @@
       <c r="C12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="D12" s="49" t="s">
         <v>493</v>
       </c>
       <c r="E12" s="1">
@@ -4282,7 +4460,7 @@
       <c r="C13" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="56" t="s">
+      <c r="D13" s="49" t="s">
         <v>493</v>
       </c>
       <c r="E13" s="1">
@@ -4306,7 +4484,7 @@
       <c r="C14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="56" t="s">
+      <c r="D14" s="49" t="s">
         <v>493</v>
       </c>
       <c r="E14" s="1">
@@ -4372,7 +4550,7 @@
       <c r="C17" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="50" t="s">
         <v>494</v>
       </c>
       <c r="E17" s="1">
@@ -4396,7 +4574,7 @@
       <c r="C18" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="58" t="s">
+      <c r="D18" s="51" t="s">
         <v>496</v>
       </c>
       <c r="E18" s="1">
@@ -4420,7 +4598,7 @@
       <c r="C19" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="51"/>
+      <c r="D19" s="44"/>
       <c r="E19" s="1">
         <v>106</v>
       </c>
@@ -4442,7 +4620,7 @@
       <c r="C20" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="44" t="s">
         <v>238</v>
       </c>
       <c r="E20" s="4">
@@ -4487,7 +4665,7 @@
       <c r="C22" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="58" t="s">
+      <c r="D22" s="51" t="s">
         <v>497</v>
       </c>
       <c r="E22" s="26">
@@ -4502,7 +4680,7 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="50">
+      <c r="A23" s="43">
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
@@ -4535,7 +4713,7 @@
       <c r="C24" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="52" t="s">
         <v>498</v>
       </c>
       <c r="E24" s="1">
@@ -4559,7 +4737,7 @@
       <c r="C25" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="59" t="s">
+      <c r="D25" s="52" t="s">
         <v>499</v>
       </c>
       <c r="E25" s="13">
@@ -4568,7 +4746,7 @@
       <c r="F25" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="78" t="s">
+      <c r="G25" s="67" t="s">
         <v>140</v>
       </c>
       <c r="H25" s="3" t="s">
@@ -4585,7 +4763,7 @@
       <c r="C26" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="D26" s="49" t="s">
         <v>510</v>
       </c>
       <c r="E26" s="1">
@@ -4594,10 +4772,12 @@
       <c r="F26" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="H26" s="3"/>
+      <c r="H26" s="3" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="22">
@@ -4714,7 +4894,7 @@
       <c r="C32" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="56" t="s">
+      <c r="D32" s="49" t="s">
         <v>510</v>
       </c>
       <c r="E32" s="1">
@@ -4840,13 +5020,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>58</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E38" s="1">
         <v>125</v>
@@ -4871,16 +5051,16 @@
       <c r="C39" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="70">
+      <c r="E39" s="61">
         <v>126</v>
       </c>
-      <c r="F39" s="71" t="s">
+      <c r="F39" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="G39" s="72" t="s">
+      <c r="G39" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="H39" s="44" t="s">
+      <c r="H39" s="77" t="s">
         <v>467</v>
       </c>
     </row>
@@ -4894,19 +5074,19 @@
       <c r="C40" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D40" s="60" t="s">
+      <c r="D40" s="53" t="s">
         <v>509</v>
       </c>
-      <c r="E40" s="70">
+      <c r="E40" s="61">
         <v>127</v>
       </c>
-      <c r="F40" s="71" t="s">
+      <c r="F40" s="62" t="s">
         <v>156</v>
       </c>
-      <c r="G40" s="72" t="s">
+      <c r="G40" s="63" t="s">
         <v>156</v>
       </c>
-      <c r="H40" s="45"/>
+      <c r="H40" s="78"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
@@ -4918,13 +5098,13 @@
       <c r="C41" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E41" s="67">
+      <c r="E41" s="58">
         <v>128</v>
       </c>
-      <c r="F41" s="68" t="s">
+      <c r="F41" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="G41" s="69" t="s">
+      <c r="G41" s="60" t="s">
         <v>157</v>
       </c>
       <c r="H41" s="1" t="s">
@@ -4938,16 +5118,16 @@
       <c r="B42" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="45" t="s">
         <v>63</v>
       </c>
       <c r="E42" s="13">
         <v>129</v>
       </c>
-      <c r="F42" s="65" t="s">
+      <c r="F42" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="G42" s="66" t="s">
+      <c r="G42" s="88" t="s">
         <v>158</v>
       </c>
       <c r="H42" s="1" t="s">
@@ -4970,10 +5150,12 @@
       <c r="F43" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="H43" s="3"/>
+      <c r="H43" s="1" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
@@ -5015,7 +5197,9 @@
       <c r="G45" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H45" s="3"/>
+      <c r="H45" s="89" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
@@ -5031,12 +5215,14 @@
         <v>133</v>
       </c>
       <c r="F46" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="G46" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H46" s="3"/>
+      <c r="H46" s="1" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
@@ -5057,7 +5243,7 @@
       <c r="G47" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="H47" s="62" t="s">
+      <c r="H47" s="83" t="s">
         <v>512</v>
       </c>
     </row>
@@ -5080,7 +5266,7 @@
       <c r="G48" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="H48" s="62"/>
+      <c r="H48" s="83"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
@@ -5155,7 +5341,7 @@
       <c r="C52" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D52" s="60" t="s">
+      <c r="D52" s="53" t="s">
         <v>509</v>
       </c>
       <c r="E52" s="1">
@@ -5179,16 +5365,16 @@
       <c r="C53" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="D53" s="60" t="s">
+      <c r="D53" s="53" t="s">
         <v>509</v>
       </c>
       <c r="E53" s="1">
         <v>140</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="90" t="s">
         <v>169</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="19" t="s">
         <v>170</v>
       </c>
       <c r="H53" s="3"/>
@@ -5224,6 +5410,9 @@
       <c r="C55" s="3" t="s">
         <v>76</v>
       </c>
+      <c r="D55" s="3" t="s">
+        <v>566</v>
+      </c>
       <c r="E55" s="22">
         <v>142</v>
       </c>
@@ -5233,7 +5422,7 @@
       <c r="G55" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="H55" s="60" t="s">
+      <c r="H55" s="53" t="s">
         <v>509</v>
       </c>
     </row>
@@ -5247,7 +5436,7 @@
       <c r="C56" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D56" s="60" t="s">
+      <c r="D56" s="53" t="s">
         <v>509</v>
       </c>
       <c r="E56" s="22">
@@ -5265,14 +5454,14 @@
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="82" t="s">
+      <c r="B57" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="83" t="s">
+      <c r="C57" s="71" t="s">
         <v>78</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E57" s="22">
         <v>144</v>
@@ -5283,7 +5472,7 @@
       <c r="G57" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="H57" s="60" t="s">
+      <c r="H57" s="53" t="s">
         <v>513</v>
       </c>
     </row>
@@ -5339,7 +5528,7 @@
       <c r="C60" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="60" t="s">
+      <c r="D60" s="53" t="s">
         <v>509</v>
       </c>
       <c r="E60" s="1">
@@ -5363,7 +5552,7 @@
       <c r="C61" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="60" t="s">
+      <c r="D61" s="53" t="s">
         <v>509</v>
       </c>
       <c r="E61" s="1">
@@ -5378,14 +5567,17 @@
       <c r="H61" s="3"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="1">
+      <c r="A62" s="5">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="71" t="s">
         <v>83</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>560</v>
       </c>
       <c r="E62" s="1">
         <v>149</v>
@@ -5439,11 +5631,11 @@
       <c r="G64" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H64" s="60" t="s">
+      <c r="H64" s="53" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:11">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -5462,9 +5654,11 @@
       <c r="G65" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H65" s="3"/>
-    </row>
-    <row r="66" spans="1:9">
+      <c r="H65" s="3" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -5483,11 +5677,11 @@
       <c r="G66" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="H66" s="60" t="s">
+      <c r="H66" s="53" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:11">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -5508,14 +5702,14 @@
       </c>
       <c r="H67" s="3"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:11">
       <c r="A68" s="13">
         <v>67</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C68" s="79" t="s">
+      <c r="C68" s="68" t="s">
         <v>53</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -5532,7 +5726,7 @@
       </c>
       <c r="H68" s="3"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:11">
       <c r="A69" s="12">
         <v>68</v>
       </c>
@@ -5551,11 +5745,11 @@
       <c r="G69" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="H69" s="60" t="s">
+      <c r="H69" s="53" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:11">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -5576,15 +5770,18 @@
       </c>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:11">
       <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="48" t="s">
         <v>94</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>561</v>
       </c>
       <c r="E71" s="1">
         <v>158</v>
@@ -5597,7 +5794,7 @@
       </c>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:11">
       <c r="A72" s="22">
         <v>71</v>
       </c>
@@ -5621,7 +5818,7 @@
       </c>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:11">
       <c r="A73" s="23">
         <v>72</v>
       </c>
@@ -5631,7 +5828,7 @@
       <c r="C73" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D73" s="60" t="s">
+      <c r="D73" s="53" t="s">
         <v>509</v>
       </c>
       <c r="E73" s="1">
@@ -5643,11 +5840,11 @@
       <c r="G73" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="H73" s="60" t="s">
+      <c r="H73" s="53" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:11">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -5657,6 +5854,9 @@
       <c r="C74" s="3" t="s">
         <v>97</v>
       </c>
+      <c r="D74" s="3" t="s">
+        <v>514</v>
+      </c>
       <c r="E74" s="1">
         <v>161</v>
       </c>
@@ -5668,7 +5868,7 @@
       </c>
       <c r="H74" s="3"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:11">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -5684,7 +5884,7 @@
       <c r="F75" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="G75" s="78" t="s">
+      <c r="G75" s="67" t="s">
         <v>196</v>
       </c>
       <c r="H75" s="3"/>
@@ -5692,11 +5892,11 @@
         <v>508</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:11">
       <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="53" t="s">
+      <c r="B76" s="46" t="s">
         <v>99</v>
       </c>
       <c r="C76" s="7" t="s">
@@ -5716,7 +5916,7 @@
       </c>
       <c r="H76" s="3"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:11">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -5737,7 +5937,7 @@
       </c>
       <c r="H77" s="3"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:11">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -5758,7 +5958,7 @@
       </c>
       <c r="H78" s="3"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:11">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -5771,25 +5971,33 @@
       <c r="E79" s="1">
         <v>166</v>
       </c>
-      <c r="F79" s="24" t="s">
+      <c r="F79" s="86" t="s">
         <v>202</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="G79" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="H79" s="3"/>
+      <c r="H79" s="3" t="s">
+        <v>555</v>
+      </c>
       <c r="I79" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="80" spans="1:9">
+      <c r="J79" t="s">
+        <v>556</v>
+      </c>
+      <c r="K79" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="54" t="s">
+      <c r="B80" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="C80" s="55" t="s">
+      <c r="C80" s="48" t="s">
         <v>103</v>
       </c>
       <c r="E80" s="22">
@@ -5864,7 +6072,7 @@
       <c r="F83" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="G83" s="77" t="s">
+      <c r="G83" s="66" t="s">
         <v>207</v>
       </c>
       <c r="H83" s="3" t="s">
@@ -5884,10 +6092,10 @@
       <c r="C84" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="E84" s="86">
+      <c r="E84" s="74">
         <v>171</v>
       </c>
-      <c r="F84" s="87" t="s">
+      <c r="F84" s="75" t="s">
         <v>208</v>
       </c>
       <c r="G84" s="7" t="s">
@@ -5935,7 +6143,7 @@
       <c r="G86" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="I86" s="51" t="s">
+      <c r="I86" s="44" t="s">
         <v>506</v>
       </c>
     </row>
@@ -5975,13 +6183,13 @@
       <c r="C88" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E88" s="70">
+      <c r="E88" s="61">
         <v>175</v>
       </c>
-      <c r="F88" s="68" t="s">
+      <c r="F88" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="G88" s="69" t="s">
+      <c r="G88" s="60" t="s">
         <v>214</v>
       </c>
       <c r="H88" s="3" t="s">
@@ -6040,7 +6248,7 @@
       <c r="B91" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C91" s="85" t="s">
+      <c r="C91" s="73" t="s">
         <v>222</v>
       </c>
       <c r="E91" s="4">
@@ -6062,7 +6270,7 @@
       <c r="B92" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C92" s="85" t="s">
+      <c r="C92" s="73" t="s">
         <v>224</v>
       </c>
       <c r="E92" s="5">
@@ -6132,8 +6340,11 @@
       <c r="B95" s="16" t="s">
         <v>468</v>
       </c>
-      <c r="C95" s="17" t="s">
+      <c r="C95" s="37" t="s">
         <v>469</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>562</v>
       </c>
       <c r="E95" s="35">
         <v>192</v>
@@ -6155,7 +6366,7 @@
       <c r="C96" s="17" t="s">
         <v>470</v>
       </c>
-      <c r="D96" s="60" t="s">
+      <c r="D96" s="53" t="s">
         <v>511</v>
       </c>
       <c r="E96" s="35">
@@ -6227,7 +6438,7 @@
       <c r="G99" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="H99" s="61" t="s">
+      <c r="H99" s="54" t="s">
         <v>488</v>
       </c>
     </row>
@@ -6241,43 +6452,43 @@
       <c r="C100" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="E100" s="76" t="s">
-        <v>541</v>
-      </c>
-      <c r="F100" s="76"/>
-      <c r="G100" s="76"/>
-      <c r="H100" s="76"/>
-      <c r="I100" s="76"/>
+      <c r="E100" s="85" t="s">
+        <v>539</v>
+      </c>
+      <c r="F100" s="85"/>
+      <c r="G100" s="85"/>
+      <c r="H100" s="85"/>
+      <c r="I100" s="85"/>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="45" t="s">
+      <c r="A102" s="78" t="s">
         <v>329</v>
       </c>
-      <c r="B102" s="45"/>
-      <c r="C102" s="45"/>
-      <c r="D102" s="45"/>
-      <c r="E102" s="45"/>
-      <c r="F102" s="45"/>
-      <c r="G102" s="45"/>
+      <c r="B102" s="78"/>
+      <c r="C102" s="78"/>
+      <c r="D102" s="78"/>
+      <c r="E102" s="78"/>
+      <c r="F102" s="78"/>
+      <c r="G102" s="78"/>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="1">
         <v>197</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="C104" s="81" t="s">
-        <v>550</v>
+        <v>547</v>
+      </c>
+      <c r="C104" s="69" t="s">
+        <v>548</v>
       </c>
       <c r="E104" s="1">
         <v>201</v>
       </c>
       <c r="F104" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G104" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6285,19 +6496,19 @@
         <v>198</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E105" s="1">
         <v>202</v>
       </c>
       <c r="F105" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G105" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6305,19 +6516,19 @@
         <v>199</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E106" s="1">
         <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G106" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6325,19 +6536,19 @@
         <v>200</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E107" s="1">
         <v>204</v>
       </c>
       <c r="F107" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G107" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -7542,7 +7753,7 @@
     <SignatureMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#rsa-sha256"/>
     <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idPackageObject">
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>Z+l9Zf5+8RthSWVjeic74Gm/W+2hj4jGDgnPFuoYuT8=</DigestValue>
+      <DigestValue>CVbjiOm4PVCH6o1rJhXA2gSm/abNml4mbi4ZFqTC0m8=</DigestValue>
     </Reference>
     <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idOfficeObject">
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -7553,14 +7764,14 @@
         <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
       </Transforms>
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>RLGhMLDeLo+uuJjyHDR8mQUIvGqjJ+zvdNqaBu303iw=</DigestValue>
+      <DigestValue>Y7dNnED8UIUxx9ZNhbqyw2V1KRu4yelqxPGfscT4Bbg=</DigestValue>
     </Reference>
   </SignedInfo>
-  <SignatureValue>YFUutrQC/1h4Zb1SfTMLCbZc+16b3zDLU1N8DoaajcX+upkVbjeMCuRks3Ric52hCzaQbvQw+m+t
-Y8kIBIwpZ+/XYSjxwaXJkxJVkdA8CloJ4Vk6X8j0W0NAaz0P7C0DPyXifLZMbk2BX2qxpn3Sg6Xl
-VzMgwI1cwygx0ZOPWLhQKZ0IuYKpBWjF5kQ4hJ8P2ydEHX7I90U0FB/3II4+FxcZL8gedsaBOwbX
-LSMbmT9ilFPDzbIvd9H+dPe7oAsMo44+ttekPawtjAjriPX7iqdTeEKevT7WNaCr0XyzJMFhUn52
-jVcHfVHulrPB6Bk2ZGdYhmiLXizNoN4hPVlwOQ==</SignatureValue>
+  <SignatureValue>hEY1AxgyGiKHx6N+lb4baY1+pr2EreOG18MkiRZjBI9UZECbt6kqPJ9hroTuzVnumI6xSWRF2Oyv
+ToVgWItP75IETUnAGE+n+U5/Y6R98y3KEScKWqzT/YCnKUBfIkbFOo676mm+xP9LbdskXikxig3G
+9SDD/R9fil/Xds9Zs8jWLQaSTGXjso9g3Iti18C7R5KlYO4UcCsrjGQXGXxUt8IaS+q30W9oanm+
+tSIKBhpctBhMWEPg+FjDRT6mumhIsrndgBoh0eIe/SdVtV/CNAkyyg8yR3LxTSIAy1alY0ySVDTb
+kAkSRmQ5h+N+c5g8p5sxUKiIMUXIqm1OTWBnrg==</SignatureValue>
   <KeyInfo>
     <X509Data>
       <X509Certificate>MIIDujCCAqKgAwIBAgIK3DAIbS5AItImsDANBgkqhkiG9w0BAQsFADCBijEiMCAGA1UEAwwZ5LqR5aSp5piO5a6H5a6Z57O757ufVUNYTjEbMBkGA1UEChMSQU1EIFJ5emVuIDkgNzk0MEhYMRcwFQYDVQQLDA5RUee+pDY4MDQ2NDM2NTEhMB8GCSqGSIb3DQEJARYSNTAxNDMwMDQxQGJpbGliaWxpMQswCQYDVQQGEwJDTjAeFw0yNDA4MTIwMzExNDdaFw0yOTA4MTIwMzExNDdaMIGKMSIwIAYDVQQDDBnkupHlpKnmmI7lroflrpnns7vnu59VQ1hOMRswGQYDVQQKExJBTUQgUnl6ZW4gOSA3OTQwSFgxFzAVBgNVBAsMDlFR576kNjgwNDY0MzY1MSEwHwYJKoZIhvcNAQkBFhI1MDE0MzAwNDFAYmlsaWJpbGkxCzAJBgNVBAYTAkNOMIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA3hfxo46kNdl/MdVB15fJk0bD09CGechP9Xma8mSzh228fHNc/kXpCXDrcX4br/0b7gsOwZqI+YigaoBKJjMbFpT1dfMr7PRCmdWyGhcTJ18ROTczbYvGhYbz3pLcIcIk3tHNLzxjOfpmxTW5FaysUAdxpHrZ4SmhQtytFJD9A3qVSH860pNU1kRc3wK2M3nc0n5YAWUKzAX/upg8xhzXqjFvQrAJvyDwTcr+/y9TMM8A8qZbG6STBM2fpRZb5fIW+6xBdVVfwQ7odJLjZ4X2Mlqv1P3T3GazSZRHZHAtGrpPjVGYNs/5AE9jW7Vmc/4XhODQIYS4ULl9+yPMcyBbLwIDAQABoyAwHjAPBgkqhkiG9y8BAQoEAgUAMAsGA1UdDwQEAwIDmDANBgkqhkiG9w0BAQsFAAOCAQEAOCVHM+GIGHW7JvfyOrYBwPbTfubNFF9vWqxnOR1Eu1mAnPYcRiDkGwPEkX3kDq32CjR1wBanvHXzjJgkoY8TzxwAJZRnOE+MUjOQhlJ7RV7IG11QL52DKPvOZrYsUAG5gpOZ1VKxC3OewBwQ1TROcl9uVY0nOBrpNgyzkNZwE3JcKdKkBL1n3DQxQC1zHuNZ/AxYyH+GNNg90kP4xMEr/JunlWH/5cEM2rIwqI2o8pErx5dns56Ri/J9P2BzXUJ87h0nFePfEr/r/afCeMh5zYP6iZOkZdTSR4WSPBQsp0DmwbbeViyFQ0qkchqDsFktbDJ6s6SzfG0R3u6ZmAaE9g==</X509Certificate>
@@ -7687,11 +7898,11 @@
       </Reference>
       <Reference URI="/xl/sharedStrings.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sharedStrings+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>1pHEF1e8IHQZm8yQdHFpEPFHVozPAwU6NIOoMO1NSpc=</DigestValue>
+        <DigestValue>sZRQJbHAuM7gfOSzgfRknrECmJL/AusZNhrWuG157EU=</DigestValue>
       </Reference>
       <Reference URI="/xl/styles.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.styles+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>dMXhcFQ/rv1VrsXBLgrcIcTCus+5PPKW/xG2ioDmAaE=</DigestValue>
+        <DigestValue>kXNqlnvaEqH4QjdX4gFzbx58GnWeIuXnxVoCQMpoL2k=</DigestValue>
       </Reference>
       <Reference URI="/xl/theme/theme1.xml?ContentType=application/vnd.openxmlformats-officedocument.theme+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -7699,20 +7910,20 @@
       </Reference>
       <Reference URI="/xl/workbook.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sheet.main+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>4zB8vyD/e3HPSq9vWGx7ELsPQylvJTh4s8t6kbLv+7w=</DigestValue>
+        <DigestValue>jQgIWwvcdy7UqHIILtwdGt2BG1TuYgloQ/sjpiPV19c=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/_rels/sheet1.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>BvH/o/r1aBi6K/7k1gXIW4XRyL4xhdvV0Wm/eT8Krg8=</DigestValue>
+        <DigestValue>VcFWf3FkbLzbM9PeAnkswiJtp1jIGDeZyRnERp7NX8Y=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/_rels/sheet2.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
@@ -7756,15 +7967,15 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet1.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>WAv5tjGaqxe4w2TjWQysku2X5uy5ZOK4FnHIZQsz0DQ=</DigestValue>
+        <DigestValue>e3Kyqs7Zz3iuzGX9MnnNSuTxkL/Vn74av+dolJUTkAU=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet2.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>KML7ch+wn4vX0MI0dYHzUspcWf0+X99Nn7e42nJx/a4=</DigestValue>
+        <DigestValue>MzzeimqhlZVn4csPyXrpl1Vxlz3UUGak/YKvU7YCFSo=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet3.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>iSDp6w9x3ZI6wWDvwgGj/tpnxH7zXdFOt4w5y5msY7I=</DigestValue>
+        <DigestValue>duFs3Xd2nW9hQx4uApy/P+sygsaByALTn+XoKAvrkwQ=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet4.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -7772,7 +7983,7 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet5.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>K6XmtaUZRSlyMB95sZ37aIgO3KUQtFlUvIsERF5PNHw=</DigestValue>
+        <DigestValue>bZ6pEiqAjmhAg4Q3aOy75UnFxW0uAynN8N6OnwBNpRU=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet6.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -7780,14 +7991,14 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet7.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>TEsr1PymJtx4qSRuYZrPgeLLXQsFSZQ7rFu6IBr/XFg=</DigestValue>
+        <DigestValue>Wapfr764Wz8eUOMAkoJoYnZUgsPo8v5w/hjsRB7DKBw=</DigestValue>
       </Reference>
     </Manifest>
     <SignatureProperties>
       <SignatureProperty Id="idSignatureTime" Target="#idPackageSignature">
         <mdssi:SignatureTime xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature">
           <mdssi:Format>YYYY-MM-DDThh:mm:ssTZD</mdssi:Format>
-          <mdssi:Value>2026-04-12T12:59:25Z</mdssi:Value>
+          <mdssi:Value>2026-04-13T11:44:53Z</mdssi:Value>
         </mdssi:SignatureTime>
       </SignatureProperty>
     </SignatureProperties>
@@ -7819,7 +8030,7 @@
     <xd:QualifyingProperties xmlns:xd="http://uri.etsi.org/01903/v1.3.2#" Target="#idPackageSignature">
       <xd:SignedProperties Id="idSignedProperties">
         <xd:SignedSignatureProperties>
-          <xd:SigningTime>2026-04-12T12:59:25Z</xd:SigningTime>
+          <xd:SigningTime>2026-04-13T11:44:53Z</xd:SigningTime>
           <xd:SigningCertificate>
             <xd:Cert>
               <xd:CertDigest>

--- a/PCDN域名URL关键字.xlsx
+++ b/PCDN域名URL关键字.xlsx
@@ -5,10 +5,10 @@
   <workbookPr autoCompressPictures="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\QQ文件\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\下载\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:201_{CD7AEB3A-01FD-4B1F-A3D3-BBDA6C1EB8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:201_{B7C8033C-F308-4807-BD91-DC9C08089EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" activeTab="2" xr2:uid="{635FD1CB-08EF-4A62-AA24-FB7602255245}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="595">
   <si>
     <t>序号</t>
   </si>
@@ -2010,12 +2010,99 @@
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>bcache</t>
+  </si>
+  <si>
+    <t>gdfs</t>
+  </si>
+  <si>
+    <t>dataflow</t>
+  </si>
+  <si>
+    <t>dm</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dm.snssdk.com</t>
+  </si>
+  <si>
+    <t>ks-sh</t>
+  </si>
+  <si>
+    <t>vccdn</t>
+  </si>
+  <si>
+    <t>vccdn-tos</t>
+  </si>
+  <si>
+    <t>bdxiguavod</t>
+  </si>
+  <si>
+    <t>yfdts</t>
+  </si>
+  <si>
+    <t>yfscdn</t>
+  </si>
+  <si>
+    <t>v4.kwaicdn</t>
+  </si>
+  <si>
+    <t>v4.kwaicdn.com</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.dcdn</t>
+  </si>
+  <si>
+    <t>dcdn</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>bdurl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>mcs</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>msc.snssdk.com</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>或许影响隐私</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dig.bdurl.net</t>
+  </si>
+  <si>
+    <t>广告、双刃剑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>awemeughun</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>应该只是广告</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>sf3-ttcdn-tos.pstatp.com</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.nodeseek.com/post-387541-1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="64">
+  <fonts count="65">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2553,6 +2640,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="38">
     <fill>
@@ -3012,7 +3107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3262,6 +3357,15 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3292,14 +3396,11 @@
     <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="42" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -4193,7 +4294,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBFF6F1-A409-4FB7-99BD-5BD2847458F8}">
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="7.92578125" style="1" customWidth="1"/>
@@ -4222,10 +4323,10 @@
         <v>219</v>
       </c>
       <c r="H1" s="3"/>
-      <c r="I1" s="83" t="s">
+      <c r="I1" s="86" t="s">
         <v>220</v>
       </c>
-      <c r="J1" s="83"/>
+      <c r="J1" s="86"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="22">
@@ -4237,18 +4338,18 @@
       <c r="C2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="85" t="s">
+      <c r="D2" s="88" t="s">
         <v>498</v>
       </c>
-      <c r="F2" s="86" t="s">
+      <c r="F2" s="89" t="s">
         <v>235</v>
       </c>
-      <c r="G2" s="86"/>
+      <c r="G2" s="89"/>
       <c r="H2" s="12"/>
-      <c r="I2" s="87" t="s">
+      <c r="I2" s="90" t="s">
         <v>549</v>
       </c>
-      <c r="J2" s="87"/>
+      <c r="J2" s="90"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="22">
@@ -4260,7 +4361,7 @@
       <c r="C3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="85"/>
+      <c r="D3" s="88"/>
       <c r="E3" s="1">
         <v>90</v>
       </c>
@@ -4273,10 +4374,10 @@
       <c r="H3" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="I3" s="88" t="s">
+      <c r="I3" s="91" t="s">
         <v>234</v>
       </c>
-      <c r="J3" s="88"/>
+      <c r="J3" s="91"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="22">
@@ -4288,7 +4389,7 @@
       <c r="C4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="85"/>
+      <c r="D4" s="88"/>
       <c r="E4" s="1">
         <v>91</v>
       </c>
@@ -4301,10 +4402,10 @@
       <c r="H4" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="I4" s="89" t="s">
+      <c r="I4" s="92" t="s">
         <v>240</v>
       </c>
-      <c r="J4" s="89"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="12">
@@ -4347,7 +4448,7 @@
         <v>118</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="91" t="s">
+      <c r="I6" s="94" t="s">
         <v>541</v>
       </c>
     </row>
@@ -4374,7 +4475,7 @@
         <v>119</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="91"/>
+      <c r="I7" s="94"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="22">
@@ -4399,7 +4500,7 @@
         <v>120</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="91"/>
+      <c r="I8" s="94"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="23">
@@ -4424,7 +4525,7 @@
         <v>121</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="91"/>
+      <c r="I9" s="94"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="22">
@@ -4449,7 +4550,7 @@
         <v>122</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="91"/>
+      <c r="I10" s="94"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="22">
@@ -5082,10 +5183,10 @@
       <c r="E38" s="1">
         <v>125</v>
       </c>
-      <c r="F38" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="G38" s="7" t="s">
+      <c r="F38" s="96" t="s">
+        <v>593</v>
+      </c>
+      <c r="G38" s="85" t="s">
         <v>154</v>
       </c>
       <c r="H38" s="1" t="s">
@@ -5111,7 +5212,7 @@
       <c r="G39" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="H39" s="84" t="s">
+      <c r="H39" s="87" t="s">
         <v>467</v>
       </c>
     </row>
@@ -5137,7 +5238,7 @@
       <c r="G40" s="63" t="s">
         <v>156</v>
       </c>
-      <c r="H40" s="85"/>
+      <c r="H40" s="88"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
@@ -5294,7 +5395,7 @@
       <c r="G47" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="H47" s="90" t="s">
+      <c r="H47" s="93" t="s">
         <v>510</v>
       </c>
     </row>
@@ -5317,7 +5418,7 @@
       <c r="G48" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="H48" s="90"/>
+      <c r="H48" s="93"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
@@ -5849,10 +5950,10 @@
       <c r="A72" s="22">
         <v>71</v>
       </c>
-      <c r="B72" s="94" t="s">
+      <c r="B72" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="C72" s="95" t="s">
+      <c r="C72" s="85" t="s">
         <v>95</v>
       </c>
       <c r="D72" s="3" t="s">
@@ -6391,7 +6492,7 @@
       <c r="B95" s="16" t="s">
         <v>568</v>
       </c>
-      <c r="C95" s="93" t="s">
+      <c r="C95" s="83" t="s">
         <v>569</v>
       </c>
       <c r="D95" s="3" t="s">
@@ -6503,24 +6604,24 @@
       <c r="C100" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="E100" s="92" t="s">
+      <c r="E100" s="95" t="s">
         <v>534</v>
       </c>
-      <c r="F100" s="92"/>
-      <c r="G100" s="92"/>
-      <c r="H100" s="92"/>
-      <c r="I100" s="92"/>
+      <c r="F100" s="95"/>
+      <c r="G100" s="95"/>
+      <c r="H100" s="95"/>
+      <c r="I100" s="95"/>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="85" t="s">
+      <c r="A102" s="88" t="s">
         <v>329</v>
       </c>
-      <c r="B102" s="85"/>
-      <c r="C102" s="85"/>
-      <c r="D102" s="85"/>
-      <c r="E102" s="85"/>
-      <c r="F102" s="85"/>
-      <c r="G102" s="85"/>
+      <c r="B102" s="88"/>
+      <c r="C102" s="88"/>
+      <c r="D102" s="88"/>
+      <c r="E102" s="88"/>
+      <c r="F102" s="88"/>
+      <c r="G102" s="88"/>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="1">
@@ -6538,7 +6639,7 @@
       <c r="F104" t="s">
         <v>535</v>
       </c>
-      <c r="G104" t="s">
+      <c r="G104" s="3" t="s">
         <v>536</v>
       </c>
     </row>
@@ -6558,7 +6659,7 @@
       <c r="F105" t="s">
         <v>537</v>
       </c>
-      <c r="G105" t="s">
+      <c r="G105" s="3" t="s">
         <v>537</v>
       </c>
     </row>
@@ -6578,7 +6679,7 @@
       <c r="F106" t="s">
         <v>538</v>
       </c>
-      <c r="G106" t="s">
+      <c r="G106" s="3" t="s">
         <v>538</v>
       </c>
     </row>
@@ -6598,9 +6699,161 @@
       <c r="F107" t="s">
         <v>539</v>
       </c>
-      <c r="G107" t="s">
+      <c r="G107" s="3" t="s">
         <v>540</v>
       </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="1">
+        <v>205</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E108" s="1">
+        <v>212</v>
+      </c>
+      <c r="F108" t="s">
+        <v>572</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="1">
+        <v>206</v>
+      </c>
+      <c r="B109" t="s">
+        <v>586</v>
+      </c>
+      <c r="C109" s="73" t="s">
+        <v>587</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="E109" s="1">
+        <v>213</v>
+      </c>
+      <c r="F109" t="s">
+        <v>573</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="1">
+        <v>207</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E110" s="1">
+        <v>214</v>
+      </c>
+      <c r="F110" t="s">
+        <v>577</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="1">
+        <v>208</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="E111" s="1">
+        <v>215</v>
+      </c>
+      <c r="F111" t="s">
+        <v>579</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="1">
+        <v>209</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="E112" s="1">
+        <v>216</v>
+      </c>
+      <c r="F112" t="s">
+        <v>582</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="1">
+        <v>210</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="E113" s="1">
+        <v>217</v>
+      </c>
+      <c r="F113" t="s">
+        <v>589</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="1">
+        <v>211</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E114" s="1">
+        <v>218</v>
+      </c>
+      <c r="F114" t="s">
+        <v>591</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="H114" s="44" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="B115" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -7085,7 +7338,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004E8C14-01FA-4F79-B5F4-D85F586C9EEB}">
-  <dimension ref="A1:A141"/>
+  <dimension ref="A1:A142"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="21.0703125" customWidth="1"/>
@@ -7127,672 +7380,680 @@
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>330</v>
+      <c r="A9" s="97" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
         <v>465</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A9" r:id="rId1" xr:uid="{A6200C11-2711-4A4A-BD83-8CC05E0B3745}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7804,7 +8065,7 @@
     <SignatureMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#rsa-sha256"/>
     <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idPackageObject">
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>VzqFLO+IYRufohWyWQ7RUjZRo1gI2b8coj2z/x4VmLM=</DigestValue>
+      <DigestValue>OIEMf+G/meQ4ydpodbit/PM6eJSUndCY21R1AE/cW5Q=</DigestValue>
     </Reference>
     <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idOfficeObject">
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -7815,14 +8076,14 @@
         <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
       </Transforms>
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>1eoPhkK7j/9677vNaCKAQilP9RSIoT2JTqIdtV1M810=</DigestValue>
+      <DigestValue>j6YF+XV1BbtNq9ON7MUz7Vq3qS5LztqQe5d3o8h/jrk=</DigestValue>
     </Reference>
   </SignedInfo>
-  <SignatureValue>S4HGiEkkaevCaQ9T1Rfi31UWeFJYytE9ctu3K5fo0ZWcWbIElftOLZu5oyeM0zBNzb9WGDclRp3B
-Z7+7aSRR9k3ZDY5MnHjaB+h/lPXWkcv2i9tXGyawi5vPqk5oEjWWGHOoZo3cRivX1ArAiSpi9j0D
-nIdtlfVnX/0xXZ6wEnLLNnlMojeuTlkeOIZ95kWeQ3Bzv+/5wV96YrNbm9rkl0/Z3wOtCg0cBmM0
-xRyUUwomnmya6YivMcjyrzXyLsp8UJhm7AFY/L6GRKz8TIsgk1Gr/81VJOzXqa75NkOk5kcQkrnq
-kGTOpgTRXUw3zJXRyxATnOTPLdtJoy9DYravyA==</SignatureValue>
+  <SignatureValue>KQ69cm3gq7sjJnXe3wAZClncrkwLH9VY7phS1fkN0bgHyzkXNOe0yAwM6mx/iRGXrCZYy0pNDHIc
+rVxVMmAJoqygoyRQUUN0QCQp8NLUfGPhOzQcKA8hFdfp7Q29bPDjLxsLRb/5OjlWJuswKnOQGEV8
+awOX+/4sdhTOKFS2/ON4UAMr6AVWgWxvBp+eD8UENhP/e9O3CbqwsLf73qoSIAY2X97ReMfI/Ezg
+OzwvRlQ/dBHs0n64nxh+oBNh9T1vZjFnCV6uascS/GrHyYu5NovJWcnW95rqclazh7XyOprvvoih
+i/PRZHCV6J98SSD431mMwg4HfwYbxD8ArqGZjg==</SignatureValue>
   <KeyInfo>
     <X509Data>
       <X509Certificate>MIIDujCCAqKgAwIBAgIK3DAIbS5AItImsDANBgkqhkiG9w0BAQsFADCBijEiMCAGA1UEAwwZ5LqR5aSp5piO5a6H5a6Z57O757ufVUNYTjEbMBkGA1UEChMSQU1EIFJ5emVuIDkgNzk0MEhYMRcwFQYDVQQLDA5RUee+pDY4MDQ2NDM2NTEhMB8GCSqGSIb3DQEJARYSNTAxNDMwMDQxQGJpbGliaWxpMQswCQYDVQQGEwJDTjAeFw0yNDA4MTIwMzExNDdaFw0yOTA4MTIwMzExNDdaMIGKMSIwIAYDVQQDDBnkupHlpKnmmI7lroflrpnns7vnu59VQ1hOMRswGQYDVQQKExJBTUQgUnl6ZW4gOSA3OTQwSFgxFzAVBgNVBAsMDlFR576kNjgwNDY0MzY1MSEwHwYJKoZIhvcNAQkBFhI1MDE0MzAwNDFAYmlsaWJpbGkxCzAJBgNVBAYTAkNOMIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA3hfxo46kNdl/MdVB15fJk0bD09CGechP9Xma8mSzh228fHNc/kXpCXDrcX4br/0b7gsOwZqI+YigaoBKJjMbFpT1dfMr7PRCmdWyGhcTJ18ROTczbYvGhYbz3pLcIcIk3tHNLzxjOfpmxTW5FaysUAdxpHrZ4SmhQtytFJD9A3qVSH860pNU1kRc3wK2M3nc0n5YAWUKzAX/upg8xhzXqjFvQrAJvyDwTcr+/y9TMM8A8qZbG6STBM2fpRZb5fIW+6xBdVVfwQ7odJLjZ4X2Mlqv1P3T3GazSZRHZHAtGrpPjVGYNs/5AE9jW7Vmc/4XhODQIYS4ULl9+yPMcyBbLwIDAQABoyAwHjAPBgkqhkiG9y8BAQoEAgUAMAsGA1UdDwQEAwIDmDANBgkqhkiG9w0BAQsFAAOCAQEAOCVHM+GIGHW7JvfyOrYBwPbTfubNFF9vWqxnOR1Eu1mAnPYcRiDkGwPEkX3kDq32CjR1wBanvHXzjJgkoY8TzxwAJZRnOE+MUjOQhlJ7RV7IG11QL52DKPvOZrYsUAG5gpOZ1VKxC3OewBwQ1TROcl9uVY0nOBrpNgyzkNZwE3JcKdKkBL1n3DQxQC1zHuNZ/AxYyH+GNNg90kP4xMEr/JunlWH/5cEM2rIwqI2o8pErx5dns56Ri/J9P2BzXUJ87h0nFePfEr/r/afCeMh5zYP6iZOkZdTSR4WSPBQsp0DmwbbeViyFQ0qkchqDsFktbDJ6s6SzfG0R3u6ZmAaE9g==</X509Certificate>
@@ -7843,6 +8104,7 @@
       <Reference URI="/xl/_rels/workbook.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId9"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId8"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
@@ -7852,7 +8114,6 @@
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId6"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId5"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId10"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
@@ -7872,9 +8133,9 @@
       <Reference URI="/xl/drawings/_rels/drawing2.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
@@ -7894,9 +8155,9 @@
       <Reference URI="/xl/drawings/_rels/drawing4.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
@@ -7949,11 +8210,11 @@
       </Reference>
       <Reference URI="/xl/sharedStrings.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sharedStrings+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>b9DUsSxrSd68wJXJ1rMXsoaJ+GucvXNTv5nxcBJLmJQ=</DigestValue>
+        <DigestValue>th/0fKv1PafVN4uzmm7oi5Cn5aZ+BuEjzL7E61AfnO0=</DigestValue>
       </Reference>
       <Reference URI="/xl/styles.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.styles+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>XDar2hPDfIYzh/F/bIy4e4ql7z8bIKAcFFiA8ZtdfXc=</DigestValue>
+        <DigestValue>XmzTv0Qx7ve/VjpzC50a9tHTJl30vgmGa54Bxt9ZiOE=</DigestValue>
       </Reference>
       <Reference URI="/xl/theme/theme1.xml?ContentType=application/vnd.openxmlformats-officedocument.theme+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -7961,15 +8222,15 @@
       </Reference>
       <Reference URI="/xl/workbook.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sheet.main+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>vbWz9rxp9JNDt/UHrQtdIVS6fm+wItd2iPug/4qlUfg=</DigestValue>
+        <DigestValue>WGLtziaa5K97YXWhFWjjMcmKNFQcWOBA5Aj4yIgh6RQ=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/_rels/sheet1.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
@@ -8016,6 +8277,16 @@
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
         <DigestValue>y+WpNtGIt12R9jLFTmLLn89fEeCDfd6tGhw18EoAHwU=</DigestValue>
       </Reference>
+      <Reference URI="/xl/worksheets/_rels/sheet7.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
+        <Transforms>
+          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+          </Transform>
+          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+        </Transforms>
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
+        <DigestValue>1Un34tChQjAlTPIuKfZ/LUZvgv4QqyFLUKvYV7WWKJU=</DigestValue>
+      </Reference>
       <Reference URI="/xl/worksheets/sheet1.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
         <DigestValue>IUjARVelW85HcEMYqrq31wR+cwQlLiFk6k1G1alW3mA=</DigestValue>
@@ -8026,7 +8297,7 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet3.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>g0rswf1HD+RhMkZZXeJ/4/fRN65qMddYL2nvZDN8baE=</DigestValue>
+        <DigestValue>R8CEyjjTp+X1E7OxdnFue8E+t0Dt0ygoffdfAfC4Q7I=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet4.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8042,14 +8313,14 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet7.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>Wapfr764Wz8eUOMAkoJoYnZUgsPo8v5w/hjsRB7DKBw=</DigestValue>
+        <DigestValue>EXdbl7OdPZlET3mSKphU4esf5o3KiJrizcUKfYUr/IM=</DigestValue>
       </Reference>
     </Manifest>
     <SignatureProperties>
       <SignatureProperty Id="idSignatureTime" Target="#idPackageSignature">
         <mdssi:SignatureTime xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature">
           <mdssi:Format>YYYY-MM-DDThh:mm:ssTZD</mdssi:Format>
-          <mdssi:Value>2026-04-13T12:02:35Z</mdssi:Value>
+          <mdssi:Value>2026-04-13T13:46:59Z</mdssi:Value>
         </mdssi:SignatureTime>
       </SignatureProperty>
     </SignatureProperties>
@@ -8081,7 +8352,7 @@
     <xd:QualifyingProperties xmlns:xd="http://uri.etsi.org/01903/v1.3.2#" Target="#idPackageSignature">
       <xd:SignedProperties Id="idSignedProperties">
         <xd:SignedSignatureProperties>
-          <xd:SigningTime>2026-04-13T12:02:35Z</xd:SigningTime>
+          <xd:SigningTime>2026-04-13T13:46:59Z</xd:SigningTime>
           <xd:SigningCertificate>
             <xd:Cert>
               <xd:CertDigest>

--- a/PCDN域名URL关键字.xlsx
+++ b/PCDN域名URL关键字.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30019"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\下载\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\QQ文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:201_{B7C8033C-F308-4807-BD91-DC9C08089EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BA5546-986B-4ADB-AD4B-84717B96C6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="tbWAkON66rsCtxC9Qha3fAyz9cES2rxhc3K/qePta4z56wUb4PWV1u/3ysk/KSQmGONimK8o4EL91T/saHT0aA==" workbookSaltValue="wGRIzkB9/tJ0EQZiuruSQg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" activeTab="2" xr2:uid="{635FD1CB-08EF-4A62-AA24-FB7602255245}"/>
   </bookViews>
   <sheets>
-    <sheet name="更新说明" sheetId="7" r:id="rId1"/>
+    <sheet name="更新说明" sheetId="8" r:id="rId1"/>
     <sheet name="IP ACL（高级）" sheetId="2" r:id="rId2"/>
     <sheet name="PCDN域名" sheetId="1" r:id="rId3"/>
     <sheet name="Hosts" sheetId="3" r:id="rId4"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="602">
   <si>
     <t>序号</t>
   </si>
@@ -1071,9 +1072,6 @@
     <t>! --- 列表来源(https://raw.githubusercontent.com/privacy-protection-tools/anti-AD/refs/heads/master/discretion/pcdn.txt) ---</t>
   </si>
   <si>
-    <t>! --- 列表来源[哥哥科技](https://space.bilibili.com/501430041) ---</t>
-  </si>
-  <si>
     <t>! 自定义过滤清单 - 综合优化版 (全量合并去重)</t>
   </si>
   <si>
@@ -1159,9 +1157,6 @@
   </si>
   <si>
     <t>@@||xiaohongshu.com^$important</t>
-  </si>
-  <si>
-    <t>@@||xhscdn.com^$important</t>
   </si>
   <si>
     <t>! ---------- [2. 关键词抑制：广谱拦截 PCDN 厂商] ----------</t>
@@ -1966,18 +1961,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>v. 4.2.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>第16次修订（阶段性主要版本）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.04.13 20时</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>疑似也影响nVIDIA驱动下载更新</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2095,6 +2078,54 @@
   </si>
   <si>
     <t>https://www.nodeseek.com/post-387541-1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>影响番茄系应用</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注：为什么只更新，几乎不删？完整日志保留，避免暗箱操作</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>影响WPS、小红书</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>第17次修订（阶段性主要版本）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.22 18时</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 4.2.2r</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>! --- 列表来源[哥哥科技](https://space.bilibili.com/501430041) ---</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>@@||*.xhscdn.com^$important</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>@@||*.wpscdn.cn^$important</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>@@||*.wpscdn.com^$important</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>建议设置</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>不过要按照实际情况</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2649,7 +2680,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2859,6 +2890,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -3107,7 +3150,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3204,9 +3247,6 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3366,6 +3406,30 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="42" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="42" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3395,12 +3459,6 @@
     </xf>
     <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="42" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3468,25 +3526,20 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>23587</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>668552</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="1945808" cy="2552700"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="图片 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA787E49-B3A9-C34C-1B81-2EFB8E00BF8A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DFF7664-0F96-46EC-993A-26828C4585E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3509,7 +3562,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3229430" y="0"/>
+          <a:off x="720273" y="0"/>
           <a:ext cx="1945808" cy="2552700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3528,7 +3581,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4172,7 +4225,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8876E99-BF81-4B8D-842A-096E4511FCE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B0E35B-6A7A-48D2-B1DB-8AF96A63466D}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
@@ -4182,99 +4235,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="42.9" customHeight="1">
-      <c r="A1" s="64" t="s">
-        <v>554</v>
+      <c r="A1" s="63" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="60.45" customHeight="1">
-      <c r="A2" s="77" t="s">
-        <v>553</v>
-      </c>
-      <c r="D2" s="55" t="s">
-        <v>548</v>
+      <c r="A2" s="76" t="s">
+        <v>551</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>564</v>
+        <v>595</v>
       </c>
       <c r="D4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="D6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="D8" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="56"/>
+      <c r="A10" s="55"/>
       <c r="D10" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="D16" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>521</v>
-      </c>
-      <c r="D17" s="65" t="s">
-        <v>527</v>
+        <v>519</v>
+      </c>
+      <c r="D17" s="64" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="B19" s="72" t="s">
-        <v>547</v>
+      <c r="B19" s="71" t="s">
+        <v>545</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="V//mbyVfulZ+rvmoE6C41Y9kSBELfS+BP8io5PhXRb9JGsh9mC8uyu5MCu6HwQu+HKeywqMKmKq+qNWdEKfGzQ==" saltValue="vVreuo4BHIfTfUtkGg5PmA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" insertColumns="0" insertRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5VPW2B9F0BM83kTZDycFtKXimZYK3UNj7Cc/ReI9FjFoQdglSGCVxIBt0v1+qZk1iPqqsDZe6vptcOF6Uo/GTg==" saltValue="kR1j5DJzosdhWqNwHY/H9g==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" pivotTables="0"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" display="『哥哥科技』" xr:uid="{9EF32144-521B-4950-AE15-70DA5D0081D6}"/>
-    <hyperlink ref="D17" r:id="rId2" xr:uid="{B96BC5BE-4A8D-4A8F-A8FE-74CA9E53C7B5}"/>
-    <hyperlink ref="A2" r:id="rId3" display="https://qun.qq.com/universal-share/share?ac=1&amp;authKey=%2FWJ%2F4NS6lNp1cyU2a1kUo%2F%2FEfq8vD6q7SXUux2UosjZ%2BialqZVNe%2Bk3w1YoOUR3b&amp;busi_data=eyJncm91cENvZGUiOiI2ODA0NjQzNjUiLCJ0b2tlbiI6IkI5ZHVYaHJnSGlZZEpzSkRhamdOZFZaNy9aZFJ1L1JwNGpZYWNJWTJJRThGYjBoVjN6RUxhUkcvV0h4eHBwV2siLCJ1aW4iOiIxNTIwMDg1MjQ5In0%3D&amp;data=iHLL1DGOGIhddoSRjGmI9D2bMbNLa4vwx5YfZQAzvPM0sAuYo67cPN4265_UAPSpbgqWLVl8vmWBZVREf_Qg-g&amp;svctype=4&amp;tempid=h5_group_info" xr:uid="{32AB89CA-61C1-4DD7-8B95-E91924B9D322}"/>
+    <hyperlink ref="D17" r:id="rId1" xr:uid="{24C562C0-6387-4B63-98CE-3C9E3FAF2EE4}"/>
+    <hyperlink ref="A1" r:id="rId2" display="『哥哥科技』" xr:uid="{34360349-868F-442B-9309-5DDB2E2EA2C2}"/>
+    <hyperlink ref="A2" r:id="rId3" display="https://qun.qq.com/universal-share/share?ac=1&amp;authKey=%2FWJ%2F4NS6lNp1cyU2a1kUo%2F%2FEfq8vD6q7SXUux2UosjZ%2BialqZVNe%2Bk3w1YoOUR3b&amp;busi_data=eyJncm91cENvZGUiOiI2ODA0NjQzNjUiLCJ0b2tlbiI6IkI5ZHVYaHJnSGlZZEpzSkRhamdOZFZaNy9aZFJ1L1JwNGpZYWNJWTJJRThGYjBoVjN6RUxhUkcvV0h4eHBwV2siLCJ1aW4iOiIxNTIwMDg1MjQ5In0%3D&amp;data=iHLL1DGOGIhddoSRjGmI9D2bMbNLa4vwx5YfZQAzvPM0sAuYo67cPN4265_UAPSpbgqWLVl8vmWBZVREf_Qg-g&amp;svctype=4&amp;tempid=h5_group_info" xr:uid="{762486EC-3F1C-4561-BBFC-7A0E8CD46672}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId4"/>
@@ -4294,7 +4347,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBFF6F1-A409-4FB7-99BD-5BD2847458F8}">
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="7.92578125" style="1" customWidth="1"/>
@@ -4323,10 +4376,10 @@
         <v>219</v>
       </c>
       <c r="H1" s="3"/>
-      <c r="I1" s="86" t="s">
+      <c r="I1" s="93" t="s">
         <v>220</v>
       </c>
-      <c r="J1" s="86"/>
+      <c r="J1" s="93"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="22">
@@ -4338,18 +4391,18 @@
       <c r="C2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="88" t="s">
-        <v>498</v>
-      </c>
-      <c r="F2" s="89" t="s">
+      <c r="D2" s="95" t="s">
+        <v>496</v>
+      </c>
+      <c r="F2" s="96" t="s">
         <v>235</v>
       </c>
-      <c r="G2" s="89"/>
+      <c r="G2" s="96"/>
       <c r="H2" s="12"/>
-      <c r="I2" s="90" t="s">
-        <v>549</v>
-      </c>
-      <c r="J2" s="90"/>
+      <c r="I2" s="97" t="s">
+        <v>547</v>
+      </c>
+      <c r="J2" s="97"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="22">
@@ -4361,7 +4414,7 @@
       <c r="C3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="88"/>
+      <c r="D3" s="95"/>
       <c r="E3" s="1">
         <v>90</v>
       </c>
@@ -4372,12 +4425,12 @@
         <v>115</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="I3" s="91" t="s">
+        <v>498</v>
+      </c>
+      <c r="I3" s="98" t="s">
         <v>234</v>
       </c>
-      <c r="J3" s="91"/>
+      <c r="J3" s="98"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="22">
@@ -4389,23 +4442,23 @@
       <c r="C4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="88"/>
+      <c r="D4" s="95"/>
       <c r="E4" s="1">
         <v>91</v>
       </c>
-      <c r="F4" s="80" t="s">
+      <c r="F4" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="81" t="s">
+      <c r="G4" s="80" t="s">
         <v>116</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="I4" s="92" t="s">
+        <v>559</v>
+      </c>
+      <c r="I4" s="99" t="s">
         <v>240</v>
       </c>
-      <c r="J4" s="92"/>
+      <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="12">
@@ -4441,15 +4494,15 @@
       <c r="E6" s="1">
         <v>93</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F6" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="47" t="s">
         <v>118</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="94" t="s">
-        <v>541</v>
+      <c r="I6" s="101" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4462,8 +4515,8 @@
       <c r="C7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="49" t="s">
-        <v>491</v>
+      <c r="D7" s="48" t="s">
+        <v>489</v>
       </c>
       <c r="E7" s="1">
         <v>94</v>
@@ -4475,7 +4528,7 @@
         <v>119</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="94"/>
+      <c r="I7" s="101"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="22">
@@ -4487,8 +4540,8 @@
       <c r="C8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="49" t="s">
-        <v>491</v>
+      <c r="D8" s="48" t="s">
+        <v>489</v>
       </c>
       <c r="E8" s="1">
         <v>95</v>
@@ -4500,7 +4553,7 @@
         <v>120</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="94"/>
+      <c r="I8" s="101"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="23">
@@ -4512,8 +4565,8 @@
       <c r="C9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="49" t="s">
-        <v>491</v>
+      <c r="D9" s="48" t="s">
+        <v>489</v>
       </c>
       <c r="E9" s="1">
         <v>96</v>
@@ -4525,7 +4578,7 @@
         <v>121</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="94"/>
+      <c r="I9" s="101"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="22">
@@ -4537,8 +4590,8 @@
       <c r="C10" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>491</v>
+      <c r="D10" s="48" t="s">
+        <v>489</v>
       </c>
       <c r="E10" s="22">
         <v>97</v>
@@ -4546,11 +4599,11 @@
       <c r="F10" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="36" t="s">
         <v>122</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="94"/>
+      <c r="I10" s="101"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="22">
@@ -4562,13 +4615,13 @@
       <c r="C11" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="49" t="s">
-        <v>491</v>
+      <c r="D11" s="48" t="s">
+        <v>489</v>
       </c>
       <c r="E11" s="22">
         <v>98</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="35" t="s">
         <v>123</v>
       </c>
       <c r="G11" s="17" t="s">
@@ -4586,8 +4639,8 @@
       <c r="C12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="49" t="s">
-        <v>491</v>
+      <c r="D12" s="48" t="s">
+        <v>489</v>
       </c>
       <c r="E12" s="1">
         <v>99</v>
@@ -4610,8 +4663,8 @@
       <c r="C13" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="49" t="s">
-        <v>491</v>
+      <c r="D13" s="48" t="s">
+        <v>489</v>
       </c>
       <c r="E13" s="1">
         <v>100</v>
@@ -4634,8 +4687,8 @@
       <c r="C14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="49" t="s">
-        <v>491</v>
+      <c r="D14" s="48" t="s">
+        <v>489</v>
       </c>
       <c r="E14" s="1">
         <v>101</v>
@@ -4698,10 +4751,10 @@
         <v>28</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>493</v>
-      </c>
-      <c r="D17" s="50" t="s">
-        <v>492</v>
+        <v>491</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>490</v>
       </c>
       <c r="E17" s="1">
         <v>104</v>
@@ -4724,8 +4777,8 @@
       <c r="C18" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="51" t="s">
-        <v>494</v>
+      <c r="D18" s="50" t="s">
+        <v>492</v>
       </c>
       <c r="E18" s="1">
         <v>105</v>
@@ -4748,7 +4801,7 @@
       <c r="C19" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="44"/>
+      <c r="D19" s="43"/>
       <c r="E19" s="1">
         <v>106</v>
       </c>
@@ -4770,7 +4823,7 @@
       <c r="C20" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="43" t="s">
         <v>238</v>
       </c>
       <c r="E20" s="4">
@@ -4815,8 +4868,8 @@
       <c r="C22" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="51" t="s">
-        <v>495</v>
+      <c r="D22" s="50" t="s">
+        <v>493</v>
       </c>
       <c r="E22" s="26">
         <v>109</v>
@@ -4828,21 +4881,21 @@
         <v>135</v>
       </c>
       <c r="H22" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="43">
+      <c r="A23" s="42">
         <v>22</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="33" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E23" s="22">
         <v>110</v>
@@ -4865,8 +4918,8 @@
       <c r="C24" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="52" t="s">
-        <v>496</v>
+      <c r="D24" s="51" t="s">
+        <v>494</v>
       </c>
       <c r="E24" s="1">
         <v>111</v>
@@ -4889,8 +4942,8 @@
       <c r="C25" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="52" t="s">
-        <v>497</v>
+      <c r="D25" s="51" t="s">
+        <v>495</v>
       </c>
       <c r="E25" s="13">
         <v>112</v>
@@ -4898,7 +4951,7 @@
       <c r="F25" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="67" t="s">
+      <c r="G25" s="66" t="s">
         <v>140</v>
       </c>
       <c r="H25" s="3" t="s">
@@ -4915,8 +4968,8 @@
       <c r="C26" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="49" t="s">
-        <v>508</v>
+      <c r="D26" s="48" t="s">
+        <v>506</v>
       </c>
       <c r="E26" s="1">
         <v>113</v>
@@ -4928,7 +4981,7 @@
         <v>141</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5046,19 +5099,21 @@
       <c r="C32" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="49" t="s">
-        <v>508</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D32" s="48" t="s">
+        <v>506</v>
+      </c>
+      <c r="E32" s="13">
         <v>119</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="H32" s="3"/>
+      <c r="H32" s="43" t="s">
+        <v>590</v>
+      </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
@@ -5143,7 +5198,7 @@
         <v>151</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -5172,25 +5227,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>58</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E38" s="1">
         <v>125</v>
       </c>
-      <c r="F38" s="96" t="s">
-        <v>593</v>
-      </c>
-      <c r="G38" s="85" t="s">
+      <c r="F38" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="G38" s="84" t="s">
         <v>154</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -5203,17 +5258,17 @@
       <c r="C39" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="61">
+      <c r="E39" s="60">
         <v>126</v>
       </c>
-      <c r="F39" s="62" t="s">
+      <c r="F39" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="G39" s="63" t="s">
+      <c r="G39" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="H39" s="87" t="s">
-        <v>467</v>
+      <c r="H39" s="94" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -5226,19 +5281,19 @@
       <c r="C40" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D40" s="53" t="s">
-        <v>507</v>
-      </c>
-      <c r="E40" s="61">
+      <c r="D40" s="52" t="s">
+        <v>505</v>
+      </c>
+      <c r="E40" s="60">
         <v>127</v>
       </c>
-      <c r="F40" s="62" t="s">
+      <c r="F40" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="G40" s="63" t="s">
+      <c r="G40" s="62" t="s">
         <v>156</v>
       </c>
-      <c r="H40" s="88"/>
+      <c r="H40" s="95"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
@@ -5250,17 +5305,17 @@
       <c r="C41" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E41" s="58">
+      <c r="E41" s="57">
         <v>128</v>
       </c>
-      <c r="F41" s="59" t="s">
+      <c r="F41" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="G41" s="60" t="s">
+      <c r="G41" s="59" t="s">
         <v>157</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -5270,20 +5325,20 @@
       <c r="B42" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C42" s="45" t="s">
+      <c r="C42" s="44" t="s">
         <v>63</v>
       </c>
       <c r="E42" s="13">
         <v>129</v>
       </c>
-      <c r="F42" s="57" t="s">
+      <c r="F42" s="56" t="s">
         <v>158</v>
       </c>
       <c r="G42" s="17" t="s">
         <v>158</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -5302,11 +5357,11 @@
       <c r="F43" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G43" s="73" t="s">
+      <c r="G43" s="72" t="s">
         <v>159</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5349,8 +5404,8 @@
       <c r="G45" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H45" s="78" t="s">
-        <v>560</v>
+      <c r="H45" s="77" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -5367,13 +5422,13 @@
         <v>133</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="G46" s="82" t="s">
+        <v>557</v>
+      </c>
+      <c r="G46" s="81" t="s">
         <v>162</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -5395,8 +5450,8 @@
       <c r="G47" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="H47" s="93" t="s">
-        <v>510</v>
+      <c r="H47" s="100" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5418,7 +5473,7 @@
       <c r="G48" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="H48" s="93"/>
+      <c r="H48" s="100"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
@@ -5493,8 +5548,8 @@
       <c r="C52" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D52" s="53" t="s">
-        <v>507</v>
+      <c r="D52" s="52" t="s">
+        <v>505</v>
       </c>
       <c r="E52" s="1">
         <v>139</v>
@@ -5517,13 +5572,13 @@
       <c r="C53" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="D53" s="53" t="s">
-        <v>507</v>
+      <c r="D53" s="52" t="s">
+        <v>505</v>
       </c>
       <c r="E53" s="1">
         <v>140</v>
       </c>
-      <c r="F53" s="79" t="s">
+      <c r="F53" s="78" t="s">
         <v>169</v>
       </c>
       <c r="G53" s="19" t="s">
@@ -5535,11 +5590,14 @@
       <c r="A54" s="22">
         <v>53</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="70" t="s">
         <v>75</v>
+      </c>
+      <c r="D54" s="44" t="s">
+        <v>592</v>
       </c>
       <c r="E54" s="22">
         <v>141</v>
@@ -5563,7 +5621,7 @@
         <v>76</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E55" s="22">
         <v>142</v>
@@ -5574,8 +5632,8 @@
       <c r="G55" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="H55" s="53" t="s">
-        <v>507</v>
+      <c r="H55" s="52" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -5588,8 +5646,8 @@
       <c r="C56" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D56" s="53" t="s">
-        <v>507</v>
+      <c r="D56" s="52" t="s">
+        <v>505</v>
       </c>
       <c r="E56" s="22">
         <v>143</v>
@@ -5606,14 +5664,14 @@
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="70" t="s">
+      <c r="B57" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="71" t="s">
+      <c r="C57" s="70" t="s">
         <v>78</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E57" s="22">
         <v>144</v>
@@ -5624,8 +5682,8 @@
       <c r="G57" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="H57" s="53" t="s">
-        <v>511</v>
+      <c r="H57" s="52" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -5680,8 +5738,8 @@
       <c r="C60" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="53" t="s">
-        <v>507</v>
+      <c r="D60" s="52" t="s">
+        <v>505</v>
       </c>
       <c r="E60" s="1">
         <v>147</v>
@@ -5704,8 +5762,8 @@
       <c r="C61" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="53" t="s">
-        <v>507</v>
+      <c r="D61" s="52" t="s">
+        <v>505</v>
       </c>
       <c r="E61" s="1">
         <v>148</v>
@@ -5725,11 +5783,11 @@
       <c r="B62" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C62" s="71" t="s">
+      <c r="C62" s="70" t="s">
         <v>83</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E62" s="1">
         <v>149</v>
@@ -5783,8 +5841,8 @@
       <c r="G64" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H64" s="53" t="s">
-        <v>507</v>
+      <c r="H64" s="52" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5807,7 +5865,7 @@
         <v>185</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5829,8 +5887,8 @@
       <c r="G66" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="H66" s="53" t="s">
-        <v>507</v>
+      <c r="H66" s="52" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -5861,7 +5919,7 @@
       <c r="B68" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C68" s="68" t="s">
+      <c r="C68" s="67" t="s">
         <v>53</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -5897,8 +5955,8 @@
       <c r="G69" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="H69" s="53" t="s">
-        <v>507</v>
+      <c r="H69" s="52" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5926,14 +5984,14 @@
       <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="47" t="s">
+      <c r="B71" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="48" t="s">
+      <c r="C71" s="47" t="s">
         <v>94</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E71" s="1">
         <v>158</v>
@@ -5950,14 +6008,14 @@
       <c r="A72" s="22">
         <v>71</v>
       </c>
-      <c r="B72" s="84" t="s">
+      <c r="B72" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="C72" s="85" t="s">
+      <c r="C72" s="84" t="s">
         <v>95</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E72" s="1">
         <v>159</v>
@@ -5980,8 +6038,8 @@
       <c r="C73" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D73" s="53" t="s">
-        <v>507</v>
+      <c r="D73" s="52" t="s">
+        <v>505</v>
       </c>
       <c r="E73" s="1">
         <v>160</v>
@@ -5992,8 +6050,8 @@
       <c r="G73" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="H73" s="53" t="s">
-        <v>507</v>
+      <c r="H73" s="52" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6007,7 +6065,7 @@
         <v>97</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E74" s="1">
         <v>161</v>
@@ -6036,26 +6094,26 @@
       <c r="F75" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="G75" s="67" t="s">
+      <c r="G75" s="66" t="s">
         <v>196</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="46" t="s">
+      <c r="B76" s="45" t="s">
         <v>99</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>99</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E76" s="1">
         <v>163</v>
@@ -6123,33 +6181,33 @@
       <c r="E79" s="1">
         <v>166</v>
       </c>
-      <c r="F79" s="76" t="s">
+      <c r="F79" s="75" t="s">
         <v>202</v>
       </c>
-      <c r="G79" s="40" t="s">
+      <c r="G79" s="39" t="s">
         <v>202</v>
       </c>
       <c r="H79" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="I79" t="s">
+        <v>503</v>
+      </c>
+      <c r="J79" t="s">
+        <v>549</v>
+      </c>
+      <c r="K79" t="s">
         <v>550</v>
-      </c>
-      <c r="I79" t="s">
-        <v>505</v>
-      </c>
-      <c r="J79" t="s">
-        <v>551</v>
-      </c>
-      <c r="K79" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="47" t="s">
+      <c r="B80" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C80" s="48" t="s">
+      <c r="C80" s="47" t="s">
         <v>103</v>
       </c>
       <c r="E80" s="22">
@@ -6176,10 +6234,10 @@
       <c r="E81" s="1">
         <v>168</v>
       </c>
-      <c r="F81" s="36" t="s">
+      <c r="F81" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="G81" s="37" t="s">
+      <c r="G81" s="36" t="s">
         <v>204</v>
       </c>
       <c r="H81" s="3"/>
@@ -6221,17 +6279,17 @@
       <c r="E83" s="13">
         <v>170</v>
       </c>
-      <c r="F83" s="39" t="s">
+      <c r="F83" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="G83" s="66" t="s">
+      <c r="G83" s="65" t="s">
         <v>207</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -6244,10 +6302,10 @@
       <c r="C84" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="E84" s="74">
+      <c r="E84" s="73">
         <v>171</v>
       </c>
-      <c r="F84" s="75" t="s">
+      <c r="F84" s="74" t="s">
         <v>208</v>
       </c>
       <c r="G84" s="7" t="s">
@@ -6295,8 +6353,8 @@
       <c r="G86" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="I86" s="44" t="s">
-        <v>504</v>
+      <c r="I86" s="43" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -6319,10 +6377,10 @@
         <v>213</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I87" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -6335,20 +6393,20 @@
       <c r="C88" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E88" s="61">
+      <c r="E88" s="60">
         <v>175</v>
       </c>
-      <c r="F88" s="59" t="s">
+      <c r="F88" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="G88" s="60" t="s">
+      <c r="G88" s="59" t="s">
         <v>214</v>
       </c>
       <c r="H88" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="I88" t="s">
         <v>524</v>
-      </c>
-      <c r="I88" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6400,7 +6458,7 @@
       <c r="B91" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C91" s="73" t="s">
+      <c r="C91" s="72" t="s">
         <v>222</v>
       </c>
       <c r="E91" s="4">
@@ -6422,7 +6480,7 @@
       <c r="B92" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C92" s="73" t="s">
+      <c r="C92" s="72" t="s">
         <v>224</v>
       </c>
       <c r="E92" s="5">
@@ -6431,11 +6489,11 @@
       <c r="F92" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="G92" s="40" t="s">
+      <c r="G92" s="39" t="s">
         <v>231</v>
       </c>
-      <c r="H92" s="41" t="s">
-        <v>484</v>
+      <c r="H92" s="40" t="s">
+        <v>482</v>
       </c>
       <c r="I92" s="11"/>
     </row>
@@ -6481,7 +6539,7 @@
         <v>233</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I94" s="10"/>
     </row>
@@ -6490,22 +6548,22 @@
         <v>186</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>568</v>
-      </c>
-      <c r="C95" s="83" t="s">
-        <v>569</v>
+        <v>563</v>
+      </c>
+      <c r="C95" s="82" t="s">
+        <v>564</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="E95" s="35">
+        <v>555</v>
+      </c>
+      <c r="E95" s="34">
         <v>192</v>
       </c>
       <c r="F95" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -6516,19 +6574,19 @@
         <v>308</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>468</v>
-      </c>
-      <c r="D96" s="53" t="s">
-        <v>509</v>
-      </c>
-      <c r="E96" s="35">
+        <v>466</v>
+      </c>
+      <c r="D96" s="52" t="s">
+        <v>507</v>
+      </c>
+      <c r="E96" s="34">
         <v>193</v>
       </c>
       <c r="F96" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6536,19 +6594,19 @@
         <v>188</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="E97" s="35">
+        <v>467</v>
+      </c>
+      <c r="E97" s="34">
         <v>194</v>
       </c>
       <c r="F97" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6556,19 +6614,19 @@
         <v>189</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E98" s="27">
         <v>195</v>
       </c>
-      <c r="F98" s="38" t="s">
-        <v>477</v>
+      <c r="F98" s="37" t="s">
+        <v>475</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="16.3">
@@ -6576,22 +6634,22 @@
         <v>190</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E99" s="27">
         <v>196</v>
       </c>
-      <c r="F99" s="38" t="s">
-        <v>479</v>
+      <c r="F99" s="37" t="s">
+        <v>477</v>
       </c>
       <c r="G99" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="H99" s="54" t="s">
-        <v>486</v>
+        <v>478</v>
+      </c>
+      <c r="H99" s="53" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6599,48 +6657,48 @@
         <v>191</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="E100" s="95" t="s">
-        <v>534</v>
-      </c>
-      <c r="F100" s="95"/>
-      <c r="G100" s="95"/>
-      <c r="H100" s="95"/>
-      <c r="I100" s="95"/>
+        <v>480</v>
+      </c>
+      <c r="E100" s="102" t="s">
+        <v>532</v>
+      </c>
+      <c r="F100" s="102"/>
+      <c r="G100" s="102"/>
+      <c r="H100" s="102"/>
+      <c r="I100" s="102"/>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="88" t="s">
+      <c r="A102" s="95" t="s">
         <v>329</v>
       </c>
-      <c r="B102" s="88"/>
-      <c r="C102" s="88"/>
-      <c r="D102" s="88"/>
-      <c r="E102" s="88"/>
-      <c r="F102" s="88"/>
-      <c r="G102" s="88"/>
+      <c r="B102" s="95"/>
+      <c r="C102" s="95"/>
+      <c r="D102" s="95"/>
+      <c r="E102" s="95"/>
+      <c r="F102" s="95"/>
+      <c r="G102" s="95"/>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="1">
         <v>197</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="C104" s="69" t="s">
-        <v>543</v>
+        <v>540</v>
+      </c>
+      <c r="C104" s="68" t="s">
+        <v>541</v>
       </c>
       <c r="E104" s="1">
         <v>201</v>
       </c>
       <c r="F104" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6648,19 +6706,19 @@
         <v>198</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E105" s="1">
         <v>202</v>
       </c>
       <c r="F105" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6668,19 +6726,19 @@
         <v>199</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E106" s="1">
         <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6688,19 +6746,19 @@
         <v>200</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E107" s="1">
         <v>204</v>
       </c>
       <c r="F107" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6708,19 +6766,19 @@
         <v>205</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="E108" s="1">
         <v>212</v>
       </c>
       <c r="F108" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6728,22 +6786,22 @@
         <v>206</v>
       </c>
       <c r="B109" t="s">
-        <v>586</v>
-      </c>
-      <c r="C109" s="73" t="s">
-        <v>587</v>
+        <v>581</v>
+      </c>
+      <c r="C109" s="72" t="s">
+        <v>582</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E109" s="1">
         <v>213</v>
       </c>
       <c r="F109" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6751,19 +6809,19 @@
         <v>207</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E110" s="1">
         <v>214</v>
       </c>
       <c r="F110" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6771,19 +6829,19 @@
         <v>208</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E111" s="1">
         <v>215</v>
       </c>
       <c r="F111" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -6791,19 +6849,19 @@
         <v>209</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="E112" s="1">
         <v>216</v>
       </c>
       <c r="F112" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -6811,22 +6869,22 @@
         <v>210</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E113" s="1">
         <v>217</v>
       </c>
       <c r="F113" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G113" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="H113" s="1" t="s">
         <v>585</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6834,26 +6892,31 @@
         <v>211</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E114" s="1">
         <v>218</v>
       </c>
       <c r="F114" t="s">
+        <v>586</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="H114" s="43" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="B115" s="43"/>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="B117" s="43" t="s">
         <v>591</v>
       </c>
-      <c r="G114" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="H114" s="44" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="B115" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -6879,88 +6942,95 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5643989-3925-447D-B127-301179B5A86C}">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="47.0703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="37" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" s="92" t="s">
+        <v>600</v>
+      </c>
+      <c r="C1" s="90" t="s">
+        <v>601</v>
+      </c>
+      <c r="D1" s="91"/>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>251</v>
       </c>
@@ -7305,11 +7375,11 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="42" t="s">
-        <v>472</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>487</v>
+      <c r="A22" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="B22" s="41" t="s">
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -7338,7 +7408,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004E8C14-01FA-4F79-B5F4-D85F586C9EEB}">
-  <dimension ref="A1:A142"/>
+  <dimension ref="A1:A144"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="21.0703125" customWidth="1"/>
@@ -7346,7 +7416,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="31" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7375,13 +7445,13 @@
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="32" t="s">
-        <v>335</v>
+      <c r="A8" s="89" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="97" t="s">
-        <v>594</v>
+      <c r="A9" s="86" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -7391,12 +7461,12 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -7406,653 +7476,664 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>365</v>
+      <c r="A42" s="88" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>366</v>
+      <c r="A43" s="88" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>367</v>
+      <c r="A44" s="88" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>465</v>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A9" r:id="rId1" xr:uid="{A6200C11-2711-4A4A-BD83-8CC05E0B3745}"/>
+    <hyperlink ref="A8" r:id="rId2" xr:uid="{5C1C5EA0-1476-4744-AC7E-066E736D1C51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8065,25 +8146,25 @@
     <SignatureMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#rsa-sha256"/>
     <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idPackageObject">
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>OIEMf+G/meQ4ydpodbit/PM6eJSUndCY21R1AE/cW5Q=</DigestValue>
+      <DigestValue>Pto5w5i8AZUHz/06nB8nPM+3L7toi9a+1m8ajG+ssrQ=</DigestValue>
     </Reference>
     <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idOfficeObject">
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>7l/PeoXgMdW/OQbDO2vbKSFs5zEAvFtWbVnMGWMXCe0=</DigestValue>
+      <DigestValue>oCBQAtpoyafaweHEDwFxC/pjsxAfRiTXl4lH4955Qek=</DigestValue>
     </Reference>
     <Reference Type="http://uri.etsi.org/01903#SignedProperties" URI="#idSignedProperties">
       <Transforms>
         <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
       </Transforms>
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>j6YF+XV1BbtNq9ON7MUz7Vq3qS5LztqQe5d3o8h/jrk=</DigestValue>
+      <DigestValue>Xp/jzcrsLEUga1SA2+P0goUE+qikzPx4yBGI1cYpa/M=</DigestValue>
     </Reference>
   </SignedInfo>
-  <SignatureValue>KQ69cm3gq7sjJnXe3wAZClncrkwLH9VY7phS1fkN0bgHyzkXNOe0yAwM6mx/iRGXrCZYy0pNDHIc
-rVxVMmAJoqygoyRQUUN0QCQp8NLUfGPhOzQcKA8hFdfp7Q29bPDjLxsLRb/5OjlWJuswKnOQGEV8
-awOX+/4sdhTOKFS2/ON4UAMr6AVWgWxvBp+eD8UENhP/e9O3CbqwsLf73qoSIAY2X97ReMfI/Ezg
-OzwvRlQ/dBHs0n64nxh+oBNh9T1vZjFnCV6uascS/GrHyYu5NovJWcnW95rqclazh7XyOprvvoih
-i/PRZHCV6J98SSD431mMwg4HfwYbxD8ArqGZjg==</SignatureValue>
+  <SignatureValue>C8LQiqK/VERZ3ESbUtEZNIqCY7I+zesvxarPU595WVnAYi2bN75yu3qoNfi2GxYBNPCHtJ9JjbRQ
+sT6T75vwJWSAvvPvffjA1J4Cmh8riFptPDEJjtIV+WOFIjZSiw5RpTDAQV8q7OxhVWndN9sPxA9v
+loZ0vlpjQeIfTlRS8BgJLC8PqqspOBH2CUpWx+nLlg1q+E74r2296vs80Cic/3bknjTbOzM/r6m9
+SHC3V1TjiRb2YCpJ09JDi4QfuQyy6kx/om1pXkDryz8nYec2ABeytKGSNYer0Lp+ksxyLtIcOAii
+WnDIWVwC4aWuSCsn0+uo/jXZ3+65V+z04igaeA==</SignatureValue>
   <KeyInfo>
     <X509Data>
       <X509Certificate>MIIDujCCAqKgAwIBAgIK3DAIbS5AItImsDANBgkqhkiG9w0BAQsFADCBijEiMCAGA1UEAwwZ5LqR5aSp5piO5a6H5a6Z57O757ufVUNYTjEbMBkGA1UEChMSQU1EIFJ5emVuIDkgNzk0MEhYMRcwFQYDVQQLDA5RUee+pDY4MDQ2NDM2NTEhMB8GCSqGSIb3DQEJARYSNTAxNDMwMDQxQGJpbGliaWxpMQswCQYDVQQGEwJDTjAeFw0yNDA4MTIwMzExNDdaFw0yOTA4MTIwMzExNDdaMIGKMSIwIAYDVQQDDBnkupHlpKnmmI7lroflrpnns7vnu59VQ1hOMRswGQYDVQQKExJBTUQgUnl6ZW4gOSA3OTQwSFgxFzAVBgNVBAsMDlFR576kNjgwNDY0MzY1MSEwHwYJKoZIhvcNAQkBFhI1MDE0MzAwNDFAYmlsaWJpbGkxCzAJBgNVBAYTAkNOMIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA3hfxo46kNdl/MdVB15fJk0bD09CGechP9Xma8mSzh228fHNc/kXpCXDrcX4br/0b7gsOwZqI+YigaoBKJjMbFpT1dfMr7PRCmdWyGhcTJ18ROTczbYvGhYbz3pLcIcIk3tHNLzxjOfpmxTW5FaysUAdxpHrZ4SmhQtytFJD9A3qVSH860pNU1kRc3wK2M3nc0n5YAWUKzAX/upg8xhzXqjFvQrAJvyDwTcr+/y9TMM8A8qZbG6STBM2fpRZb5fIW+6xBdVVfwQ7odJLjZ4X2Mlqv1P3T3GazSZRHZHAtGrpPjVGYNs/5AE9jW7Vmc/4XhODQIYS4ULl9+yPMcyBbLwIDAQABoyAwHjAPBgkqhkiG9y8BAQoEAgUAMAsGA1UdDwQEAwIDmDANBgkqhkiG9w0BAQsFAAOCAQEAOCVHM+GIGHW7JvfyOrYBwPbTfubNFF9vWqxnOR1Eu1mAnPYcRiDkGwPEkX3kDq32CjR1wBanvHXzjJgkoY8TzxwAJZRnOE+MUjOQhlJ7RV7IG11QL52DKPvOZrYsUAG5gpOZ1VKxC3OewBwQ1TROcl9uVY0nOBrpNgyzkNZwE3JcKdKkBL1n3DQxQC1zHuNZ/AxYyH+GNNg90kP4xMEr/JunlWH/5cEM2rIwqI2o8pErx5dns56Ri/J9P2BzXUJ87h0nFePfEr/r/afCeMh5zYP6iZOkZdTSR4WSPBQsp0DmwbbeViyFQ0qkchqDsFktbDJ6s6SzfG0R3u6ZmAaE9g==</X509Certificate>
@@ -8104,16 +8185,16 @@
       <Reference URI="/xl/_rels/workbook.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId6"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId5"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId10"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId9"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId8"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId7"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId6"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId5"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId10"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
@@ -8133,9 +8214,9 @@
       <Reference URI="/xl/drawings/_rels/drawing2.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
@@ -8155,9 +8236,9 @@
       <Reference URI="/xl/drawings/_rels/drawing4.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
@@ -8166,7 +8247,7 @@
       </Reference>
       <Reference URI="/xl/drawings/drawing1.xml?ContentType=application/vnd.openxmlformats-officedocument.drawing+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>RztqTOdqo3P8XJLG3AyQyBt4e1KH8RpB6MwARCryvZk=</DigestValue>
+        <DigestValue>CmVW1B3cFZYXjMhUshxzjEpc3Kix93TWDDFYyYV2+TE=</DigestValue>
       </Reference>
       <Reference URI="/xl/drawings/drawing2.xml?ContentType=application/vnd.openxmlformats-officedocument.drawing+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8210,11 +8291,11 @@
       </Reference>
       <Reference URI="/xl/sharedStrings.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sharedStrings+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>th/0fKv1PafVN4uzmm7oi5Cn5aZ+BuEjzL7E61AfnO0=</DigestValue>
+        <DigestValue>3u5Dl4emZ03zCvtcvDzJ5Lak6GiX+gLv6eDcZK+WSfw=</DigestValue>
       </Reference>
       <Reference URI="/xl/styles.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.styles+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>XmzTv0Qx7ve/VjpzC50a9tHTJl30vgmGa54Bxt9ZiOE=</DigestValue>
+        <DigestValue>c6Oc0ehIgvvUFGd4k5lP6N45hDSYFG/NaEyP3minrjg=</DigestValue>
       </Reference>
       <Reference URI="/xl/theme/theme1.xml?ContentType=application/vnd.openxmlformats-officedocument.theme+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8222,20 +8303,20 @@
       </Reference>
       <Reference URI="/xl/workbook.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sheet.main+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>WGLtziaa5K97YXWhFWjjMcmKNFQcWOBA5Aj4yIgh6RQ=</DigestValue>
+        <DigestValue>lKlTWBiiBgRjj+NYb72f97Z0yMGq7na5hV+QAJCDXts=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/_rels/sheet1.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>VcFWf3FkbLzbM9PeAnkswiJtp1jIGDeZyRnERp7NX8Y=</DigestValue>
+        <DigestValue>OTYmckysa5BVTGOPQrmEfDLSSYFF1BUk5m9BM3u4png=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/_rels/sheet2.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
@@ -8281,15 +8362,16 @@
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>1Un34tChQjAlTPIuKfZ/LUZvgv4QqyFLUKvYV7WWKJU=</DigestValue>
+        <DigestValue>wPX2vlLI28B89pXr5F2Sz94X0MP3xKtFIyQqDuXu8S4=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet1.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>IUjARVelW85HcEMYqrq31wR+cwQlLiFk6k1G1alW3mA=</DigestValue>
+        <DigestValue>6u8dpr4Cg9d4zwgjPupnL/R9J8TNSUvJo7ndd2u0MpA=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet2.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8297,15 +8379,15 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet3.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>R8CEyjjTp+X1E7OxdnFue8E+t0Dt0ygoffdfAfC4Q7I=</DigestValue>
+        <DigestValue>dXxu5VuiXieB2FKryQrpFNKCs+QVplky6aFTxHQT87c=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet4.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>tgaUyHXE9EWVZ3sYUMsGILvKfg2Z3nYLRMAwxQnFqMw=</DigestValue>
+        <DigestValue>Nwz3HAFQKfk1k7J8QG3sUG7YQJrBSQjEH4ZmC62GfDc=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet5.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>rPKImATGTAdLS1f+VnehAD2Nw7HJf+CDqNB1ZIznfrM=</DigestValue>
+        <DigestValue>OzbxVqfimeYkvk6UVGMNo6X/lonGq2rbcNQ5T7hzEzU=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet6.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8313,14 +8395,14 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet7.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>EXdbl7OdPZlET3mSKphU4esf5o3KiJrizcUKfYUr/IM=</DigestValue>
+        <DigestValue>M5+PLpWgxLAsR59BEQ46y/GuZ7R0rt1F0Ndw8YSw6iY=</DigestValue>
       </Reference>
     </Manifest>
     <SignatureProperties>
       <SignatureProperty Id="idSignatureTime" Target="#idPackageSignature">
         <mdssi:SignatureTime xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature">
           <mdssi:Format>YYYY-MM-DDThh:mm:ssTZD</mdssi:Format>
-          <mdssi:Value>2026-04-13T13:46:59Z</mdssi:Value>
+          <mdssi:Value>2026-04-22T10:12:39Z</mdssi:Value>
         </mdssi:SignatureTime>
       </SignatureProperty>
     </SignatureProperties>
@@ -8334,8 +8416,8 @@
           <SignatureImage/>
           <SignatureComments/>
           <WindowsVersion>10.0</WindowsVersion>
-          <OfficeVersion>16.0.20006/27</OfficeVersion>
-          <ApplicationVersion>16.0.20006</ApplicationVersion>
+          <OfficeVersion>16.0.20019/27</OfficeVersion>
+          <ApplicationVersion>16.0.20019</ApplicationVersion>
           <Monitors>1</Monitors>
           <HorizontalResolution>2560</HorizontalResolution>
           <VerticalResolution>1600</VerticalResolution>
@@ -8352,7 +8434,7 @@
     <xd:QualifyingProperties xmlns:xd="http://uri.etsi.org/01903/v1.3.2#" Target="#idPackageSignature">
       <xd:SignedProperties Id="idSignedProperties">
         <xd:SignedSignatureProperties>
-          <xd:SigningTime>2026-04-13T13:46:59Z</xd:SigningTime>
+          <xd:SigningTime>2026-04-22T10:12:39Z</xd:SigningTime>
           <xd:SigningCertificate>
             <xd:Cert>
               <xd:CertDigest>

--- a/PCDN域名URL关键字.xlsx
+++ b/PCDN域名URL关键字.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30019"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\QQ文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BA5546-986B-4ADB-AD4B-84717B96C6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="tbWAkON66rsCtxC9Qha3fAyz9cES2rxhc3K/qePta4z56wUb4PWV1u/3ysk/KSQmGONimK8o4EL91T/saHT0aA==" workbookSaltValue="wGRIzkB9/tJ0EQZiuruSQg==" workbookSpinCount="100000" lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:201_{F20F2D82-DBBA-4613-8724-3BC593B44B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="9qAF2+DtxfJH00hI65oRU+eMwY9KzfEARK+RHZzYeRKsLpMPantgfdAEv0/85JmJ2vchcWrG/gL+Xm43OQEJeg==" workbookSaltValue="Y+x1Z4pLCr1D/IOjMMMUEg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" activeTab="2" xr2:uid="{635FD1CB-08EF-4A62-AA24-FB7602255245}"/>
   </bookViews>
   <sheets>
-    <sheet name="更新说明" sheetId="8" r:id="rId1"/>
-    <sheet name="IP ACL（高级）" sheetId="2" r:id="rId2"/>
+    <sheet name="IP ACL（高级）" sheetId="2" r:id="rId1"/>
+    <sheet name="更新说明" sheetId="8" r:id="rId2"/>
     <sheet name="PCDN域名" sheetId="1" r:id="rId3"/>
     <sheet name="Hosts" sheetId="3" r:id="rId4"/>
     <sheet name="海外" sheetId="4" r:id="rId5"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="605">
   <si>
     <t>序号</t>
   </si>
@@ -1109,9 +1109,6 @@
   </si>
   <si>
     <t>@@||jd.com^$important</t>
-  </si>
-  <si>
-    <t>@@||*360buyimg*^$important</t>
   </si>
   <si>
     <t>@@||*meituan.net^$important</t>
@@ -2093,18 +2090,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>第17次修订（阶段性主要版本）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.04.22 18时</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>v. 4.2.2r</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>! --- 列表来源[哥哥科技](https://space.bilibili.com/501430041) ---</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2126,6 +2111,34 @@
   </si>
   <si>
     <t>不过要按照实际情况</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>误杀“apps”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>@@||360buyimg*^$important</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>@@||deepseek.com^$important</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 4.2.3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.05.30 13时</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>第19次修订（阶段性主要版本）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vivo商店，慎用！</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3150,7 +3163,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3459,6 +3472,9 @@
     </xf>
     <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3525,67 +3541,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>23587</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1945808" cy="2552700"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DFF7664-0F96-46EC-993A-26828C4585E6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="720273" y="0"/>
-          <a:ext cx="1945808" cy="2552700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3719,6 +3674,67 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>23587</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1945808" cy="2552700"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DFF7664-0F96-46EC-993A-26828C4585E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="720273" y="0"/>
+          <a:ext cx="1945808" cy="2552700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4225,6 +4241,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC21A3EC-8929-43AF-81AB-455CC9A891B1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.15"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B0E35B-6A7A-48D2-B1DB-8AF96A63466D}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
@@ -4236,93 +4263,93 @@
   <sheetData>
     <row r="1" spans="1:4" ht="42.9" customHeight="1">
       <c r="A1" s="63" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="60.45" customHeight="1">
       <c r="A2" s="76" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D2" s="54" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="D4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="D8" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="55"/>
       <c r="D10" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D14" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="D16" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="B19" s="71" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5VPW2B9F0BM83kTZDycFtKXimZYK3UNj7Cc/ReI9FjFoQdglSGCVxIBt0v1+qZk1iPqqsDZe6vptcOF6Uo/GTg==" saltValue="kR1j5DJzosdhWqNwHY/H9g==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SWmLjaif2zNHS62CoMVZ9eVol1IoSdxNr6t1MPb2U8s0irsrCkz8ESCvo34fG56GDQXdYcSRSxj15/lx5h1gvQ==" saltValue="awjqA6oCzZhiwpc6UXWDRQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D17" r:id="rId1" xr:uid="{24C562C0-6387-4B63-98CE-3C9E3FAF2EE4}"/>
@@ -4331,17 +4358,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId4"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC21A3EC-8929-43AF-81AB-455CC9A891B1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.15"/>
-  <sheetData/>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4392,7 +4408,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="95" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F2" s="96" t="s">
         <v>235</v>
@@ -4400,7 +4416,7 @@
       <c r="G2" s="96"/>
       <c r="H2" s="12"/>
       <c r="I2" s="97" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J2" s="97"/>
     </row>
@@ -4425,7 +4441,7 @@
         <v>115</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I3" s="98" t="s">
         <v>234</v>
@@ -4453,7 +4469,7 @@
         <v>116</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I4" s="99" t="s">
         <v>240</v>
@@ -4502,7 +4518,7 @@
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="101" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4516,7 +4532,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E7" s="1">
         <v>94</v>
@@ -4541,7 +4557,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E8" s="1">
         <v>95</v>
@@ -4566,7 +4582,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="48" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E9" s="1">
         <v>96</v>
@@ -4591,7 +4607,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E10" s="22">
         <v>97</v>
@@ -4616,7 +4632,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E11" s="22">
         <v>98</v>
@@ -4640,7 +4656,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="48" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E12" s="1">
         <v>99</v>
@@ -4664,7 +4680,7 @@
         <v>21</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E13" s="1">
         <v>100</v>
@@ -4688,7 +4704,7 @@
         <v>23</v>
       </c>
       <c r="D14" s="48" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E14" s="1">
         <v>101</v>
@@ -4751,10 +4767,10 @@
         <v>28</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E17" s="1">
         <v>104</v>
@@ -4778,7 +4794,7 @@
         <v>30</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E18" s="1">
         <v>105</v>
@@ -4869,7 +4885,7 @@
         <v>35</v>
       </c>
       <c r="D22" s="50" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E22" s="26">
         <v>109</v>
@@ -4881,7 +4897,7 @@
         <v>135</v>
       </c>
       <c r="H22" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4895,7 +4911,7 @@
         <v>36</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E23" s="22">
         <v>110</v>
@@ -4919,7 +4935,7 @@
         <v>37</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E24" s="1">
         <v>111</v>
@@ -4943,7 +4959,7 @@
         <v>38</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E25" s="13">
         <v>112</v>
@@ -4969,7 +4985,7 @@
         <v>40</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E26" s="1">
         <v>113</v>
@@ -4981,7 +4997,7 @@
         <v>141</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5100,7 +5116,7 @@
         <v>48</v>
       </c>
       <c r="D32" s="48" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E32" s="13">
         <v>119</v>
@@ -5112,7 +5128,7 @@
         <v>147</v>
       </c>
       <c r="H32" s="43" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -5198,7 +5214,7 @@
         <v>151</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -5214,10 +5230,10 @@
       <c r="E37" s="1">
         <v>124</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G37" s="7" t="s">
         <v>153</v>
       </c>
       <c r="H37" s="1"/>
@@ -5227,25 +5243,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>58</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E38" s="1">
         <v>125</v>
       </c>
       <c r="F38" s="85" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G38" s="84" t="s">
         <v>154</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -5268,7 +5284,7 @@
         <v>155</v>
       </c>
       <c r="H39" s="94" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -5282,7 +5298,7 @@
         <v>60</v>
       </c>
       <c r="D40" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E40" s="60">
         <v>127</v>
@@ -5315,7 +5331,7 @@
         <v>157</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -5338,7 +5354,7 @@
         <v>158</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -5361,7 +5377,7 @@
         <v>159</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5405,7 +5421,7 @@
         <v>161</v>
       </c>
       <c r="H45" s="77" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -5422,13 +5438,13 @@
         <v>133</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G46" s="81" t="s">
         <v>162</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -5451,7 +5467,7 @@
         <v>163</v>
       </c>
       <c r="H47" s="100" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5475,7 +5491,7 @@
       </c>
       <c r="H48" s="100"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -5488,15 +5504,20 @@
       <c r="E49" s="22">
         <v>136</v>
       </c>
-      <c r="F49" s="16" t="s">
+      <c r="F49" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="G49" s="17" t="s">
+      <c r="G49" s="62" t="s">
         <v>165</v>
       </c>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="H49" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="I49" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -5517,7 +5538,7 @@
       </c>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -5538,7 +5559,7 @@
       </c>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:9">
       <c r="A52" s="22">
         <v>51</v>
       </c>
@@ -5549,7 +5570,7 @@
         <v>73</v>
       </c>
       <c r="D52" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E52" s="1">
         <v>139</v>
@@ -5562,7 +5583,7 @@
       </c>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:9">
       <c r="A53" s="22">
         <v>52</v>
       </c>
@@ -5573,7 +5594,7 @@
         <v>74</v>
       </c>
       <c r="D53" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E53" s="1">
         <v>140</v>
@@ -5586,7 +5607,7 @@
       </c>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:9">
       <c r="A54" s="22">
         <v>53</v>
       </c>
@@ -5597,7 +5618,7 @@
         <v>75</v>
       </c>
       <c r="D54" s="44" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E54" s="22">
         <v>141</v>
@@ -5610,7 +5631,7 @@
       </c>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -5621,7 +5642,7 @@
         <v>76</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E55" s="22">
         <v>142</v>
@@ -5633,10 +5654,10 @@
         <v>172</v>
       </c>
       <c r="H55" s="52" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -5647,7 +5668,7 @@
         <v>77</v>
       </c>
       <c r="D56" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E56" s="22">
         <v>143</v>
@@ -5660,7 +5681,7 @@
       </c>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -5671,7 +5692,7 @@
         <v>78</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E57" s="22">
         <v>144</v>
@@ -5683,10 +5704,10 @@
         <v>175</v>
       </c>
       <c r="H57" s="52" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -5707,7 +5728,7 @@
       </c>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -5728,7 +5749,7 @@
       </c>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -5739,7 +5760,7 @@
         <v>81</v>
       </c>
       <c r="D60" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E60" s="1">
         <v>147</v>
@@ -5752,7 +5773,7 @@
       </c>
       <c r="H60" s="3"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -5763,7 +5784,7 @@
         <v>82</v>
       </c>
       <c r="D61" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E61" s="1">
         <v>148</v>
@@ -5776,7 +5797,7 @@
       </c>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:9">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -5787,7 +5808,7 @@
         <v>83</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E62" s="1">
         <v>149</v>
@@ -5800,7 +5821,7 @@
       </c>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:9">
       <c r="A63" s="12">
         <v>62</v>
       </c>
@@ -5822,7 +5843,7 @@
       </c>
       <c r="H63" s="3"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:9">
       <c r="A64" s="22">
         <v>63</v>
       </c>
@@ -5842,7 +5863,7 @@
         <v>184</v>
       </c>
       <c r="H64" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5865,7 +5886,7 @@
         <v>185</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5888,7 +5909,7 @@
         <v>186</v>
       </c>
       <c r="H66" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -5956,7 +5977,7 @@
         <v>190</v>
       </c>
       <c r="H69" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5991,7 +6012,7 @@
         <v>94</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E71" s="1">
         <v>158</v>
@@ -6015,7 +6036,7 @@
         <v>95</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E72" s="1">
         <v>159</v>
@@ -6039,7 +6060,7 @@
         <v>96</v>
       </c>
       <c r="D73" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E73" s="1">
         <v>160</v>
@@ -6051,7 +6072,7 @@
         <v>194</v>
       </c>
       <c r="H73" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6065,7 +6086,7 @@
         <v>97</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E74" s="1">
         <v>161</v>
@@ -6099,7 +6120,7 @@
       </c>
       <c r="H75" s="3"/>
       <c r="I75" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6113,7 +6134,7 @@
         <v>99</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E76" s="1">
         <v>163</v>
@@ -6188,16 +6209,16 @@
         <v>202</v>
       </c>
       <c r="H79" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="I79" t="s">
+        <v>502</v>
+      </c>
+      <c r="J79" t="s">
         <v>548</v>
       </c>
-      <c r="I79" t="s">
-        <v>503</v>
-      </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>549</v>
-      </c>
-      <c r="K79" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -6286,10 +6307,10 @@
         <v>207</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -6354,7 +6375,7 @@
         <v>212</v>
       </c>
       <c r="I86" s="43" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -6377,10 +6398,10 @@
         <v>213</v>
       </c>
       <c r="H87" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="I87" t="s">
         <v>500</v>
-      </c>
-      <c r="I87" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -6403,10 +6424,10 @@
         <v>214</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I88" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6493,7 +6514,7 @@
         <v>231</v>
       </c>
       <c r="H92" s="40" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I92" s="11"/>
     </row>
@@ -6539,7 +6560,7 @@
         <v>233</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I94" s="10"/>
     </row>
@@ -6548,22 +6569,22 @@
         <v>186</v>
       </c>
       <c r="B95" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="C95" s="82" t="s">
         <v>563</v>
       </c>
-      <c r="C95" s="82" t="s">
-        <v>564</v>
-      </c>
       <c r="D95" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E95" s="34">
         <v>192</v>
       </c>
       <c r="F95" t="s">
+        <v>467</v>
+      </c>
+      <c r="G95" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -6574,19 +6595,19 @@
         <v>308</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D96" s="52" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E96" s="34">
         <v>193</v>
       </c>
       <c r="F96" t="s">
+        <v>469</v>
+      </c>
+      <c r="G96" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6594,19 +6615,19 @@
         <v>188</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E97" s="34">
         <v>194</v>
       </c>
       <c r="F97" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6614,19 +6635,19 @@
         <v>189</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E98" s="27">
         <v>195</v>
       </c>
       <c r="F98" s="37" t="s">
+        <v>474</v>
+      </c>
+      <c r="G98" s="17" t="s">
         <v>475</v>
-      </c>
-      <c r="G98" s="17" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="16.3">
@@ -6634,22 +6655,22 @@
         <v>190</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E99" s="27">
         <v>196</v>
       </c>
       <c r="F99" s="37" t="s">
+        <v>476</v>
+      </c>
+      <c r="G99" s="17" t="s">
         <v>477</v>
       </c>
-      <c r="G99" s="17" t="s">
-        <v>478</v>
-      </c>
       <c r="H99" s="53" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6657,13 +6678,13 @@
         <v>191</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E100" s="102" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F100" s="102"/>
       <c r="G100" s="102"/>
@@ -6686,19 +6707,19 @@
         <v>197</v>
       </c>
       <c r="B104" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="C104" s="68" t="s">
         <v>540</v>
-      </c>
-      <c r="C104" s="68" t="s">
-        <v>541</v>
       </c>
       <c r="E104" s="1">
         <v>201</v>
       </c>
       <c r="F104" t="s">
+        <v>532</v>
+      </c>
+      <c r="G104" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6706,19 +6727,19 @@
         <v>198</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>527</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>528</v>
       </c>
       <c r="E105" s="1">
         <v>202</v>
       </c>
       <c r="F105" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6726,19 +6747,19 @@
         <v>199</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E106" s="1">
         <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6746,19 +6767,19 @@
         <v>200</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="E107" s="1">
         <v>204</v>
       </c>
       <c r="F107" t="s">
+        <v>536</v>
+      </c>
+      <c r="G107" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6766,19 +6787,19 @@
         <v>205</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E108" s="1">
         <v>212</v>
       </c>
       <c r="F108" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6786,22 +6807,22 @@
         <v>206</v>
       </c>
       <c r="B109" t="s">
+        <v>580</v>
+      </c>
+      <c r="C109" s="72" t="s">
         <v>581</v>
       </c>
-      <c r="C109" s="72" t="s">
+      <c r="D109" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="E109" s="1">
         <v>213</v>
       </c>
       <c r="F109" t="s">
+        <v>567</v>
+      </c>
+      <c r="G109" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6809,19 +6830,19 @@
         <v>207</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E110" s="1">
         <v>214</v>
       </c>
       <c r="F110" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6829,19 +6850,19 @@
         <v>208</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E111" s="1">
         <v>215</v>
       </c>
       <c r="F111" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -6849,19 +6870,19 @@
         <v>209</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E112" s="1">
         <v>216</v>
       </c>
       <c r="F112" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -6869,22 +6890,22 @@
         <v>210</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>579</v>
       </c>
       <c r="E113" s="1">
         <v>217</v>
       </c>
       <c r="F113" t="s">
+        <v>583</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="H113" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="G113" s="7" t="s">
-        <v>580</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6892,22 +6913,22 @@
         <v>211</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E114" s="1">
         <v>218</v>
       </c>
       <c r="F114" t="s">
+        <v>585</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="H114" s="43" t="s">
         <v>586</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="H114" s="43" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -6915,7 +6936,7 @@
     </row>
     <row r="117" spans="1:8">
       <c r="B117" s="43" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -6953,10 +6974,10 @@
         <v>241</v>
       </c>
       <c r="B1" s="92" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C1" s="90" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D1" s="91"/>
     </row>
@@ -7376,10 +7397,10 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="41" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -7408,7 +7429,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004E8C14-01FA-4F79-B5F4-D85F586C9EEB}">
-  <dimension ref="A1:A144"/>
+  <dimension ref="A1:A145"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="21.0703125" customWidth="1"/>
@@ -7416,7 +7437,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="31" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7446,12 +7467,12 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="89" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="86" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -7500,633 +7521,638 @@
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>342</v>
+      <c r="A19" s="103" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>349</v>
+      <c r="A26" s="88" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="88" t="s">
-        <v>598</v>
+      <c r="A42" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="88" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="88" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>364</v>
+      <c r="A45" s="88" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>463</v>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -8146,25 +8172,25 @@
     <SignatureMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#rsa-sha256"/>
     <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idPackageObject">
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>Pto5w5i8AZUHz/06nB8nPM+3L7toi9a+1m8ajG+ssrQ=</DigestValue>
+      <DigestValue>/iySCV1sAc4ChOJjXW99beIeOVh8HbhHWSza7s91BQs=</DigestValue>
     </Reference>
     <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idOfficeObject">
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>oCBQAtpoyafaweHEDwFxC/pjsxAfRiTXl4lH4955Qek=</DigestValue>
+      <DigestValue>XcuY37diGVrY5098uPDIo98BZLboXKR3lsb/SKaejlI=</DigestValue>
     </Reference>
     <Reference Type="http://uri.etsi.org/01903#SignedProperties" URI="#idSignedProperties">
       <Transforms>
         <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
       </Transforms>
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>Xp/jzcrsLEUga1SA2+P0goUE+qikzPx4yBGI1cYpa/M=</DigestValue>
+      <DigestValue>9KJs+r140Cxcn3wwLkEo96vs2yO1YEDRZDFRT3DAzHk=</DigestValue>
     </Reference>
   </SignedInfo>
-  <SignatureValue>C8LQiqK/VERZ3ESbUtEZNIqCY7I+zesvxarPU595WVnAYi2bN75yu3qoNfi2GxYBNPCHtJ9JjbRQ
-sT6T75vwJWSAvvPvffjA1J4Cmh8riFptPDEJjtIV+WOFIjZSiw5RpTDAQV8q7OxhVWndN9sPxA9v
-loZ0vlpjQeIfTlRS8BgJLC8PqqspOBH2CUpWx+nLlg1q+E74r2296vs80Cic/3bknjTbOzM/r6m9
-SHC3V1TjiRb2YCpJ09JDi4QfuQyy6kx/om1pXkDryz8nYec2ABeytKGSNYer0Lp+ksxyLtIcOAii
-WnDIWVwC4aWuSCsn0+uo/jXZ3+65V+z04igaeA==</SignatureValue>
+  <SignatureValue>H6n3/EYkzhvvsS1WNzkxwPZOy89EyZIECA8s8fNuaGU2AMOS0n4ceS8HMi2yHJkTpqQiQ9Z6w+U7
+Eq64LpTI1CZFuWFIQroGJkNHQ+7LfgeFfAia/FHDGXd40Zbf/8FpFvTh3Xa9ItlXZhZub4Te1+1e
+jXHzMQmIfnl1JnHcLI2XTDFU7Km0PT3y05RG9GmHzIPhesavu3om1IxMaRCIWoWgXS3fgqJpq+yn
+KYQZfbqzy5Q5sJ0FwHl4XKK4N8nonneAnCeMqVYem5a24SoFl7El/iIUeyfGA0rdBM2KhDWRy1Gy
+05TjPnTQZ45BI6h5pEtm2BhPMFlkzuwl1YAxOA==</SignatureValue>
   <KeyInfo>
     <X509Data>
       <X509Certificate>MIIDujCCAqKgAwIBAgIK3DAIbS5AItImsDANBgkqhkiG9w0BAQsFADCBijEiMCAGA1UEAwwZ5LqR5aSp5piO5a6H5a6Z57O757ufVUNYTjEbMBkGA1UEChMSQU1EIFJ5emVuIDkgNzk0MEhYMRcwFQYDVQQLDA5RUee+pDY4MDQ2NDM2NTEhMB8GCSqGSIb3DQEJARYSNTAxNDMwMDQxQGJpbGliaWxpMQswCQYDVQQGEwJDTjAeFw0yNDA4MTIwMzExNDdaFw0yOTA4MTIwMzExNDdaMIGKMSIwIAYDVQQDDBnkupHlpKnmmI7lroflrpnns7vnu59VQ1hOMRswGQYDVQQKExJBTUQgUnl6ZW4gOSA3OTQwSFgxFzAVBgNVBAsMDlFR576kNjgwNDY0MzY1MSEwHwYJKoZIhvcNAQkBFhI1MDE0MzAwNDFAYmlsaWJpbGkxCzAJBgNVBAYTAkNOMIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA3hfxo46kNdl/MdVB15fJk0bD09CGechP9Xma8mSzh228fHNc/kXpCXDrcX4br/0b7gsOwZqI+YigaoBKJjMbFpT1dfMr7PRCmdWyGhcTJ18ROTczbYvGhYbz3pLcIcIk3tHNLzxjOfpmxTW5FaysUAdxpHrZ4SmhQtytFJD9A3qVSH860pNU1kRc3wK2M3nc0n5YAWUKzAX/upg8xhzXqjFvQrAJvyDwTcr+/y9TMM8A8qZbG6STBM2fpRZb5fIW+6xBdVVfwQ7odJLjZ4X2Mlqv1P3T3GazSZRHZHAtGrpPjVGYNs/5AE9jW7Vmc/4XhODQIYS4ULl9+yPMcyBbLwIDAQABoyAwHjAPBgkqhkiG9y8BAQoEAgUAMAsGA1UdDwQEAwIDmDANBgkqhkiG9w0BAQsFAAOCAQEAOCVHM+GIGHW7JvfyOrYBwPbTfubNFF9vWqxnOR1Eu1mAnPYcRiDkGwPEkX3kDq32CjR1wBanvHXzjJgkoY8TzxwAJZRnOE+MUjOQhlJ7RV7IG11QL52DKPvOZrYsUAG5gpOZ1VKxC3OewBwQ1TROcl9uVY0nOBrpNgyzkNZwE3JcKdKkBL1n3DQxQC1zHuNZ/AxYyH+GNNg90kP4xMEr/JunlWH/5cEM2rIwqI2o8pErx5dns56Ri/J9P2BzXUJ87h0nFePfEr/r/afCeMh5zYP6iZOkZdTSR4WSPBQsp0DmwbbeViyFQ0qkchqDsFktbDJ6s6SzfG0R3u6ZmAaE9g==</X509Certificate>
@@ -8204,24 +8230,24 @@
       <Reference URI="/xl/drawings/_rels/drawing1.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>Y+3wJOMP3JY16bEUtgml2qEIrlc/vWMqGQ/VOkXiOUI=</DigestValue>
+        <DigestValue>RkThSxCNg7xiNwWjBS+PrQD1M1idXSItw8LznHbLPrY=</DigestValue>
       </Reference>
       <Reference URI="/xl/drawings/_rels/drawing2.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>PaSXpr5x6VQRUJCe1bsBVkJE2Qr7so4oiKFQt12MLho=</DigestValue>
+        <DigestValue>x1sOCVPuR2RMxgj6s8G4M8M0hmUpR2tw9C0A7SFH8N0=</DigestValue>
       </Reference>
       <Reference URI="/xl/drawings/_rels/drawing3.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
@@ -8236,22 +8262,22 @@
       <Reference URI="/xl/drawings/_rels/drawing4.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>Dfqg1JSsahKcCmxfTqDQaS0zrGqKntUo1cgv3JoLmOo=</DigestValue>
+        <DigestValue>uUOs+EN5Coe4n7DUJI6UzILPItaFWO+4hsQS6b46510=</DigestValue>
       </Reference>
       <Reference URI="/xl/drawings/drawing1.xml?ContentType=application/vnd.openxmlformats-officedocument.drawing+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>CmVW1B3cFZYXjMhUshxzjEpc3Kix93TWDDFYyYV2+TE=</DigestValue>
+        <DigestValue>mELqMwvheVFY8lLEGbVa2UXDl4NzgwhGEbxONJRik2w=</DigestValue>
       </Reference>
       <Reference URI="/xl/drawings/drawing2.xml?ContentType=application/vnd.openxmlformats-officedocument.drawing+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>mELqMwvheVFY8lLEGbVa2UXDl4NzgwhGEbxONJRik2w=</DigestValue>
+        <DigestValue>CmVW1B3cFZYXjMhUshxzjEpc3Kix93TWDDFYyYV2+TE=</DigestValue>
       </Reference>
       <Reference URI="/xl/drawings/drawing3.xml?ContentType=application/vnd.openxmlformats-officedocument.drawing+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8261,21 +8287,21 @@
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
         <DigestValue>LBc2Ea1khfeDXJMAhAk9cWm1cab2VdvCMtCJz0ysSBc=</DigestValue>
       </Reference>
-      <Reference URI="/xl/media/image1.jpeg?ContentType=image/jpeg">
+      <Reference URI="/xl/media/image1.png?ContentType=image/png">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>o95X8kMkRCF5g+3XPP8NJcgAA9XPz7Z30H3VilJ/D+w=</DigestValue>
+        <DigestValue>exDCr8yNaW/Wb16Dl24R6sEvYxUXy5tbTBgxdi0ei5c=</DigestValue>
       </Reference>
       <Reference URI="/xl/media/image2.png?ContentType=image/png">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>exDCr8yNaW/Wb16Dl24R6sEvYxUXy5tbTBgxdi0ei5c=</DigestValue>
+        <DigestValue>+HM+rXHOlgqkMsNM/CeiOCMtV3WDktfpVtrHqY7DHs4=</DigestValue>
       </Reference>
       <Reference URI="/xl/media/image3.png?ContentType=image/png">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>+HM+rXHOlgqkMsNM/CeiOCMtV3WDktfpVtrHqY7DHs4=</DigestValue>
+        <DigestValue>yr1tK3OQm8esERZuMOkteF2psNcG+F69s9K1eT0Hwjc=</DigestValue>
       </Reference>
-      <Reference URI="/xl/media/image4.png?ContentType=image/png">
+      <Reference URI="/xl/media/image4.jpeg?ContentType=image/jpeg">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>yr1tK3OQm8esERZuMOkteF2psNcG+F69s9K1eT0Hwjc=</DigestValue>
+        <DigestValue>o95X8kMkRCF5g+3XPP8NJcgAA9XPz7Z30H3VilJ/D+w=</DigestValue>
       </Reference>
       <Reference URI="/xl/media/image5.png?ContentType=image/png">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8291,11 +8317,11 @@
       </Reference>
       <Reference URI="/xl/sharedStrings.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sharedStrings+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>3u5Dl4emZ03zCvtcvDzJ5Lak6GiX+gLv6eDcZK+WSfw=</DigestValue>
+        <DigestValue>+s4aGZPX7y6/LqxkyVSQti7Seg8HTbWjcwoDvnK2n2Y=</DigestValue>
       </Reference>
       <Reference URI="/xl/styles.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.styles+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>c6Oc0ehIgvvUFGd4k5lP6N45hDSYFG/NaEyP3minrjg=</DigestValue>
+        <DigestValue>h322m0N7JHW5I/4dGmf2WWcg0Tj/KgjpfyWhgXenEhA=</DigestValue>
       </Reference>
       <Reference URI="/xl/theme/theme1.xml?ContentType=application/vnd.openxmlformats-officedocument.theme+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8303,22 +8329,9 @@
       </Reference>
       <Reference URI="/xl/workbook.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sheet.main+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>lKlTWBiiBgRjj+NYb72f97Z0yMGq7na5hV+QAJCDXts=</DigestValue>
+        <DigestValue>+JOphbxOQsdi+Jmx+TSWC4139qHV8Oxxj1Gg2fOPrmk=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/_rels/sheet1.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
-        <Transforms>
-          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
-          </Transform>
-          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
-        </Transforms>
-        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>OTYmckysa5BVTGOPQrmEfDLSSYFF1BUk5m9BM3u4png=</DigestValue>
-      </Reference>
-      <Reference URI="/xl/worksheets/_rels/sheet2.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
@@ -8326,7 +8339,20 @@
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>lHnnYDirKb6jIxGHnqbP97pjMgmbUlToG4p69Ye0Gm8=</DigestValue>
+        <DigestValue>oY0oKg4yB0FiSyDpS+lW7ZLMeZcI5wvg+y8nqaThVbI=</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/_rels/sheet2.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
+        <Transforms>
+          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
+          </Transform>
+          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+        </Transforms>
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
+        <DigestValue>GgRkcNIbsFbArpnSAg92s51N3+QTqFQD97/fu2ylXVE=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/_rels/sheet3.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
@@ -8371,23 +8397,23 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet1.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>6u8dpr4Cg9d4zwgjPupnL/R9J8TNSUvJo7ndd2u0MpA=</DigestValue>
+        <DigestValue>MzzeimqhlZVn4csPyXrpl1Vxlz3UUGak/YKvU7YCFSo=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet2.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>MzzeimqhlZVn4csPyXrpl1Vxlz3UUGak/YKvU7YCFSo=</DigestValue>
+        <DigestValue>/xb8IQ9Rg54Q5y6CSAJQEMM7MzJ1T2HidLzeP3LVuX4=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet3.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>dXxu5VuiXieB2FKryQrpFNKCs+QVplky6aFTxHQT87c=</DigestValue>
+        <DigestValue>fPmWd7OC3EnlnSJ7vFpXkJw3pFnLQ3BtThMm8cEDlzI=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet4.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>Nwz3HAFQKfk1k7J8QG3sUG7YQJrBSQjEH4ZmC62GfDc=</DigestValue>
+        <DigestValue>Ti377gj3l1FrKi3oUr3xw+/CMksXC+FHhEfS02vkOXs=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet5.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>OzbxVqfimeYkvk6UVGMNo6X/lonGq2rbcNQ5T7hzEzU=</DigestValue>
+        <DigestValue>vge4KBiwomHXa7PQSfJN2FtPaTr8II4H+vX3rBRnN/4=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet6.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8395,14 +8421,14 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet7.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>M5+PLpWgxLAsR59BEQ46y/GuZ7R0rt1F0Ndw8YSw6iY=</DigestValue>
+        <DigestValue>2MqJDcIeA7ml1JzKyC14LVs7PY41E3DrnjtS78DPyiY=</DigestValue>
       </Reference>
     </Manifest>
     <SignatureProperties>
       <SignatureProperty Id="idSignatureTime" Target="#idPackageSignature">
         <mdssi:SignatureTime xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature">
           <mdssi:Format>YYYY-MM-DDThh:mm:ssTZD</mdssi:Format>
-          <mdssi:Value>2026-04-22T10:12:39Z</mdssi:Value>
+          <mdssi:Value>2026-05-30T05:22:18Z</mdssi:Value>
         </mdssi:SignatureTime>
       </SignatureProperty>
     </SignatureProperties>
@@ -8416,8 +8442,8 @@
           <SignatureImage/>
           <SignatureComments/>
           <WindowsVersion>10.0</WindowsVersion>
-          <OfficeVersion>16.0.20019/27</OfficeVersion>
-          <ApplicationVersion>16.0.20019</ApplicationVersion>
+          <OfficeVersion>16.0.20126/27</OfficeVersion>
+          <ApplicationVersion>16.0.20126</ApplicationVersion>
           <Monitors>1</Monitors>
           <HorizontalResolution>2560</HorizontalResolution>
           <VerticalResolution>1600</VerticalResolution>
@@ -8434,7 +8460,7 @@
     <xd:QualifyingProperties xmlns:xd="http://uri.etsi.org/01903/v1.3.2#" Target="#idPackageSignature">
       <xd:SignedProperties Id="idSignedProperties">
         <xd:SignedSignatureProperties>
-          <xd:SigningTime>2026-04-22T10:12:39Z</xd:SigningTime>
+          <xd:SigningTime>2026-05-30T05:22:18Z</xd:SigningTime>
           <xd:SigningCertificate>
             <xd:Cert>
               <xd:CertDigest>
